--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="581">
   <si>
     <t xml:space="preserve">Input</t>
   </si>
@@ -1626,6 +1626,9 @@
   </si>
   <si>
     <t xml:space="preserve">Conductance parameter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;</t>
   </si>
   <si>
     <t xml:space="preserve">water_moisture_patch</t>
@@ -10740,8 +10743,8 @@
         <v>1.2E-005</v>
       </c>
       <c r="K226" s="10" t="n">
-        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 100</f>
-        <v>0.0012</v>
+        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 10</f>
+        <v>0.00012</v>
       </c>
       <c r="L226" s="10" t="n">
         <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
@@ -10785,7 +10788,7 @@
         <v>35</v>
       </c>
       <c r="K227" s="10" t="s">
-        <v>35</v>
+        <v>535</v>
       </c>
       <c r="L227" s="10" t="s">
         <v>35</v>
@@ -10793,7 +10796,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>32</v>
@@ -10805,7 +10808,7 @@
         <v>14</v>
       </c>
       <c r="E228" s="59" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F228" s="59" t="s">
         <v>496</v>
@@ -10851,7 +10854,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>32</v>
@@ -10863,7 +10866,7 @@
         <v>488</v>
       </c>
       <c r="E229" s="59" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F229" s="59" t="s">
         <v>499</v>
@@ -10909,7 +10912,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>32</v>
@@ -10921,7 +10924,7 @@
         <v>488</v>
       </c>
       <c r="E230" s="59" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F230" s="59" t="s">
         <v>499</v>
@@ -10972,7 +10975,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>32</v>
@@ -10984,7 +10987,7 @@
         <v>488</v>
       </c>
       <c r="E231" s="59" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F231" s="59" t="s">
         <v>499</v>
@@ -11030,7 +11033,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B232" s="8" t="s">
         <v>32</v>
@@ -11042,10 +11045,10 @@
         <v>14</v>
       </c>
       <c r="E232" s="59" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F232" s="59" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G232" s="10" t="n">
         <v>1E-005</v>
@@ -11092,7 +11095,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B233" s="8" t="s">
         <v>32</v>
@@ -11104,7 +11107,7 @@
         <v>14</v>
       </c>
       <c r="E233" s="59" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F233" s="59" t="s">
         <v>499</v>
@@ -11154,7 +11157,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>32</v>
@@ -11198,7 +11201,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>32</v>
@@ -11242,7 +11245,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>32</v>
@@ -11254,7 +11257,7 @@
         <v>14</v>
       </c>
       <c r="E236" s="54" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F236" s="54" t="s">
         <v>264</v>
@@ -11285,7 +11288,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="42" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B237" s="8" t="s">
         <v>32</v>
@@ -11297,10 +11300,10 @@
         <v>14</v>
       </c>
       <c r="E237" s="43" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F237" s="43" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G237" s="10" t="n">
         <v>1E-009</v>
@@ -11324,7 +11327,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="42" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>32</v>
@@ -11336,10 +11339,10 @@
         <v>14</v>
       </c>
       <c r="E238" s="43" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F238" s="43" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G238" s="10" t="n">
         <v>1E-009</v>
@@ -11363,7 +11366,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>32</v>
@@ -11375,10 +11378,10 @@
         <v>14</v>
       </c>
       <c r="E239" s="59" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F239" s="59" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G239" s="59" t="n">
         <v>0.1</v>
@@ -21290,18 +21293,18 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
@@ -21364,7 +21367,7 @@
         <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C7" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A7,$B$2:$B$170,1,FALSE())),A7,"")</f>
@@ -21601,7 +21604,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>105</v>
@@ -21613,7 +21616,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>107</v>
@@ -21625,7 +21628,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>110</v>
@@ -21637,7 +21640,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>112</v>
@@ -21793,7 +21796,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>161</v>
@@ -21805,7 +21808,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>163</v>
@@ -21817,7 +21820,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>168</v>
@@ -21829,7 +21832,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>173</v>
@@ -21853,7 +21856,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>181</v>
@@ -21865,7 +21868,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>184</v>
@@ -21877,7 +21880,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>175</v>
@@ -22084,7 +22087,7 @@
         <v>354</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C67" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A67,$B$2:$B$170,1,FALSE())),A67,"")</f>
@@ -22096,7 +22099,7 @@
         <v>357</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C68" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A68,$B$2:$B$170,1,FALSE())),A68,"")</f>
@@ -22108,7 +22111,7 @@
         <v>359</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C69" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A69,$B$2:$B$170,1,FALSE())),A69,"")</f>
@@ -22120,7 +22123,7 @@
         <v>361</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C70" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A70,$B$2:$B$170,1,FALSE())),A70,"")</f>
@@ -22225,7 +22228,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>318</v>
@@ -22636,7 +22639,7 @@
         <v>461</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C113" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A113,$B$2:$B$170,1,FALSE())),A113,"")</f>
@@ -22801,7 +22804,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>419</v>
@@ -22813,7 +22816,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>421</v>
@@ -22825,7 +22828,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>423</v>
@@ -22837,7 +22840,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>425</v>
@@ -22897,7 +22900,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>436</v>

--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">WB_defense1</t>
   </si>
   <si>
-    <t xml:space="preserve">WB_publish1</t>
+    <t xml:space="preserve">GB_publish1</t>
   </si>
   <si>
     <t xml:space="preserve">WB_def_soil_1</t>

--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="580">
   <si>
     <t xml:space="preserve">Input</t>
   </si>
@@ -1626,9 +1626,6 @@
   </si>
   <si>
     <t xml:space="preserve">Conductance parameter </t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;</t>
   </si>
   <si>
     <t xml:space="preserve">water_moisture_patch</t>
@@ -10743,8 +10740,8 @@
         <v>1.2E-005</v>
       </c>
       <c r="K226" s="10" t="n">
-        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 10</f>
-        <v>0.00012</v>
+        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 200</f>
+        <v>0.0024</v>
       </c>
       <c r="L226" s="10" t="n">
         <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
@@ -10788,7 +10785,7 @@
         <v>35</v>
       </c>
       <c r="K227" s="10" t="s">
-        <v>535</v>
+        <v>35</v>
       </c>
       <c r="L227" s="10" t="s">
         <v>35</v>
@@ -10796,7 +10793,7 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>32</v>
@@ -10808,7 +10805,7 @@
         <v>14</v>
       </c>
       <c r="E228" s="59" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F228" s="59" t="s">
         <v>496</v>
@@ -10854,7 +10851,7 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>32</v>
@@ -10866,7 +10863,7 @@
         <v>488</v>
       </c>
       <c r="E229" s="59" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F229" s="59" t="s">
         <v>499</v>
@@ -10912,7 +10909,7 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>32</v>
@@ -10924,7 +10921,7 @@
         <v>488</v>
       </c>
       <c r="E230" s="59" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F230" s="59" t="s">
         <v>499</v>
@@ -10975,7 +10972,7 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>32</v>
@@ -10987,7 +10984,7 @@
         <v>488</v>
       </c>
       <c r="E231" s="59" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F231" s="59" t="s">
         <v>499</v>
@@ -11033,7 +11030,7 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B232" s="8" t="s">
         <v>32</v>
@@ -11045,10 +11042,10 @@
         <v>14</v>
       </c>
       <c r="E232" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="F232" s="59" t="s">
         <v>545</v>
-      </c>
-      <c r="F232" s="59" t="s">
-        <v>546</v>
       </c>
       <c r="G232" s="10" t="n">
         <v>1E-005</v>
@@ -11095,7 +11092,7 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B233" s="8" t="s">
         <v>32</v>
@@ -11107,7 +11104,7 @@
         <v>14</v>
       </c>
       <c r="E233" s="59" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F233" s="59" t="s">
         <v>499</v>
@@ -11157,7 +11154,7 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>32</v>
@@ -11201,7 +11198,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>32</v>
@@ -11245,7 +11242,7 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>32</v>
@@ -11257,7 +11254,7 @@
         <v>14</v>
       </c>
       <c r="E236" s="54" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F236" s="54" t="s">
         <v>264</v>
@@ -11288,7 +11285,7 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="42" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B237" s="8" t="s">
         <v>32</v>
@@ -11300,10 +11297,10 @@
         <v>14</v>
       </c>
       <c r="E237" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="F237" s="43" t="s">
         <v>554</v>
-      </c>
-      <c r="F237" s="43" t="s">
-        <v>555</v>
       </c>
       <c r="G237" s="10" t="n">
         <v>1E-009</v>
@@ -11327,7 +11324,7 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>32</v>
@@ -11339,10 +11336,10 @@
         <v>14</v>
       </c>
       <c r="E238" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="F238" s="43" t="s">
         <v>554</v>
-      </c>
-      <c r="F238" s="43" t="s">
-        <v>555</v>
       </c>
       <c r="G238" s="10" t="n">
         <v>1E-009</v>
@@ -11366,7 +11363,7 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>32</v>
@@ -11378,10 +11375,10 @@
         <v>14</v>
       </c>
       <c r="E239" s="59" t="s">
+        <v>557</v>
+      </c>
+      <c r="F239" s="59" t="s">
         <v>558</v>
-      </c>
-      <c r="F239" s="59" t="s">
-        <v>559</v>
       </c>
       <c r="G239" s="59" t="n">
         <v>0.1</v>
@@ -21293,18 +21290,18 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
@@ -21367,7 +21364,7 @@
         <v>159</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C7" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A7,$B$2:$B$170,1,FALSE())),A7,"")</f>
@@ -21604,7 +21601,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>105</v>
@@ -21616,7 +21613,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>107</v>
@@ -21628,7 +21625,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>110</v>
@@ -21640,7 +21637,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>112</v>
@@ -21796,7 +21793,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>161</v>
@@ -21808,7 +21805,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>163</v>
@@ -21820,7 +21817,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>168</v>
@@ -21832,7 +21829,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>173</v>
@@ -21856,7 +21853,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>181</v>
@@ -21868,7 +21865,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>184</v>
@@ -21880,7 +21877,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>175</v>
@@ -22087,7 +22084,7 @@
         <v>354</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C67" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A67,$B$2:$B$170,1,FALSE())),A67,"")</f>
@@ -22099,7 +22096,7 @@
         <v>357</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C68" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A68,$B$2:$B$170,1,FALSE())),A68,"")</f>
@@ -22111,7 +22108,7 @@
         <v>359</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C69" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A69,$B$2:$B$170,1,FALSE())),A69,"")</f>
@@ -22123,7 +22120,7 @@
         <v>361</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C70" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A70,$B$2:$B$170,1,FALSE())),A70,"")</f>
@@ -22228,7 +22225,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>318</v>
@@ -22639,7 +22636,7 @@
         <v>461</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C113" s="2" t="str">
         <f aca="false">IF(ISNA(VLOOKUP(A113,$B$2:$B$170,1,FALSE())),A113,"")</f>
@@ -22804,7 +22801,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>419</v>
@@ -22816,7 +22813,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>421</v>
@@ -22828,7 +22825,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>423</v>
@@ -22840,7 +22837,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>425</v>
@@ -22900,7 +22897,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>436</v>

--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">WB_defense1</t>
   </si>
   <si>
-    <t xml:space="preserve">GB_CNW_1</t>
+    <t xml:space="preserve">GB_1.0</t>
   </si>
   <si>
     <t xml:space="preserve">GB_CN_1</t>
@@ -11346,8 +11346,8 @@
         <v>6E-007</v>
       </c>
       <c r="K224" s="10" t="n">
-        <f aca="false">0.00001 / 10 / 5 / 10 * 6 * 5</f>
-        <v>6E-007</v>
+        <f aca="false">0.00001 / 10 / 5 / 10 * 6 * 100</f>
+        <v>1.2E-005</v>
       </c>
       <c r="L224" s="10" t="n">
         <f aca="false">0.00001 / 10 / 5 / 10 * 6 * 5</f>
@@ -11446,8 +11446,8 @@
         <v>1.2E-005</v>
       </c>
       <c r="K226" s="10" t="n">
-        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 10</f>
-        <v>0.00012</v>
+        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
+        <v>1.2E-005</v>
       </c>
       <c r="L226" s="10" t="n">
         <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 10</f>

--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">GB_CN_1</t>
   </si>
   <si>
-    <t xml:space="preserve">WB_def_soil_1</t>
+    <t xml:space="preserve">GB_soil_1.0</t>
   </si>
   <si>
     <t xml:space="preserve">root_mtg_file</t>
@@ -1770,9 +1770,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00E+00"/>
+    <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -2011,7 +2012,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2056,6 +2057,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2068,12 +2073,12 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2609,6 +2614,7 @@
       <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="N2" s="11"/>
       <c r="AX2" s="2"/>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2624,10 +2630,10 @@
       <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="10" t="s">
@@ -2648,6 +2654,7 @@
       <c r="M3" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="N3" s="11"/>
       <c r="AX3" s="2"/>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2663,66 +2670,66 @@
       <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="14" t="s">
         <v>25</v>
       </c>
       <c r="M4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="14"/>
+      <c r="N4" s="11"/>
       <c r="O4" s="15"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
       <c r="S4" s="15"/>
       <c r="T4" s="15"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="16"/>
-      <c r="AG4" s="14"/>
-      <c r="AH4" s="14"/>
-      <c r="AI4" s="14"/>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="14"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="14"/>
-      <c r="AN4" s="16"/>
-      <c r="AO4" s="14"/>
-      <c r="AP4" s="14"/>
-      <c r="AQ4" s="14"/>
-      <c r="AR4" s="14"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="14"/>
-      <c r="AU4" s="16"/>
-      <c r="AV4" s="16"/>
-      <c r="AW4" s="14"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="16"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+      <c r="AD4" s="16"/>
+      <c r="AE4" s="16"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="16"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="16"/>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="16"/>
+      <c r="AM4" s="16"/>
+      <c r="AN4" s="17"/>
+      <c r="AO4" s="16"/>
+      <c r="AP4" s="16"/>
+      <c r="AQ4" s="16"/>
+      <c r="AR4" s="16"/>
+      <c r="AS4" s="17"/>
+      <c r="AT4" s="16"/>
+      <c r="AU4" s="17"/>
+      <c r="AV4" s="17"/>
+      <c r="AW4" s="16"/>
       <c r="AX4" s="2"/>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2738,10 +2745,10 @@
       <c r="D5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -2762,6 +2769,7 @@
       <c r="M5" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="N5" s="11"/>
       <c r="AX5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2777,10 +2785,10 @@
       <c r="D6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="18" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="10" t="s">
@@ -2801,6 +2809,7 @@
       <c r="M6" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
@@ -2815,10 +2824,10 @@
       <c r="D7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>39</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -2839,9 +2848,10 @@
       <c r="M7" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -2853,10 +2863,10 @@
       <c r="D8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -2877,9 +2887,10 @@
       <c r="M8" s="10" t="n">
         <v>180</v>
       </c>
+      <c r="N8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>43</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -2891,10 +2902,10 @@
       <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -2915,9 +2926,10 @@
       <c r="M9" s="10" t="n">
         <v>0.041666667</v>
       </c>
+      <c r="N9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -2929,10 +2941,10 @@
       <c r="D10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -2953,9 +2965,10 @@
       <c r="M10" s="10" t="n">
         <v>0.041666667</v>
       </c>
+      <c r="N10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -2967,10 +2980,10 @@
       <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="22" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -2991,9 +3004,10 @@
       <c r="M11" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>49</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -3005,10 +3019,10 @@
       <c r="D12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="22" t="s">
         <v>42</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -3029,9 +3043,10 @@
       <c r="M12" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -3043,10 +3058,10 @@
       <c r="D13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G13" s="10" t="s">
@@ -3067,9 +3082,10 @@
       <c r="M13" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="21" t="s">
         <v>54</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -3081,10 +3097,10 @@
       <c r="D14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="22" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -3105,9 +3121,10 @@
       <c r="M14" s="10" t="n">
         <v>5E-009</v>
       </c>
+      <c r="N14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -3119,10 +3136,10 @@
       <c r="D15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="22" t="s">
         <v>59</v>
       </c>
       <c r="G15" s="10" t="n">
@@ -3143,9 +3160,10 @@
       <c r="M15" s="10" t="n">
         <v>10</v>
       </c>
+      <c r="N15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>60</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -3157,10 +3175,10 @@
       <c r="D16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="10" t="s">
@@ -3181,9 +3199,10 @@
       <c r="M16" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="21" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3195,10 +3214,10 @@
       <c r="D17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G17" s="10" t="s">
@@ -3219,9 +3238,10 @@
       <c r="M17" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>64</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -3233,10 +3253,10 @@
       <c r="D18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="22" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="10" t="s">
@@ -3257,9 +3277,10 @@
       <c r="M18" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="21" t="s">
         <v>66</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -3271,10 +3292,10 @@
       <c r="D19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="22" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="10" t="n">
@@ -3295,9 +3316,10 @@
       <c r="M19" s="10" t="n">
         <v>86400</v>
       </c>
+      <c r="N19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="23" t="s">
         <v>69</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -3309,10 +3331,10 @@
       <c r="D20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="10" t="s">
@@ -3333,9 +3355,10 @@
       <c r="M20" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="23" t="s">
         <v>71</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -3347,10 +3370,10 @@
       <c r="D21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="24" t="s">
         <v>39</v>
       </c>
       <c r="G21" s="10" t="n">
@@ -3371,12 +3394,13 @@
       <c r="M21" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="O21" s="24" t="s">
+      <c r="N21" s="11"/>
+      <c r="O21" s="25" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="23" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -3388,10 +3412,10 @@
       <c r="D22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G22" s="10" t="s">
@@ -3412,9 +3436,10 @@
       <c r="M22" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="23" t="s">
         <v>76</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -3426,10 +3451,10 @@
       <c r="D23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G23" s="10" t="s">
@@ -3450,9 +3475,10 @@
       <c r="M23" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -3464,10 +3490,10 @@
       <c r="D24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="10" t="s">
@@ -3488,9 +3514,10 @@
       <c r="M24" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="23" t="s">
         <v>80</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -3502,10 +3529,10 @@
       <c r="D25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G25" s="10" t="s">
@@ -3526,9 +3553,10 @@
       <c r="M25" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B26" s="8" t="s">
@@ -3540,10 +3568,10 @@
       <c r="D26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G26" s="10" t="s">
@@ -3564,9 +3592,10 @@
       <c r="M26" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="23" t="s">
         <v>84</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -3578,10 +3607,10 @@
       <c r="D27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G27" s="10" t="s">
@@ -3602,9 +3631,10 @@
       <c r="M27" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="23" t="s">
         <v>86</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -3616,10 +3646,10 @@
       <c r="D28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G28" s="10" t="n">
@@ -3640,9 +3670,10 @@
       <c r="M28" s="10" t="n">
         <v>0.33</v>
       </c>
+      <c r="N28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="23" t="s">
         <v>89</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -3654,10 +3685,10 @@
       <c r="D29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10" t="s">
@@ -3678,9 +3709,10 @@
       <c r="M29" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="23" t="s">
         <v>91</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -3692,10 +3724,10 @@
       <c r="D30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G30" s="10" t="s">
@@ -3716,9 +3748,10 @@
       <c r="M30" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="23" t="s">
         <v>93</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -3730,10 +3763,10 @@
       <c r="D31" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="24" t="s">
         <v>35</v>
       </c>
       <c r="G31" s="10" t="s">
@@ -3754,9 +3787,10 @@
       <c r="M31" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="26" t="s">
         <v>95</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -3768,10 +3802,10 @@
       <c r="D32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G32" s="10" t="s">
@@ -3792,9 +3826,10 @@
       <c r="M32" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="26" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -3806,33 +3841,34 @@
       <c r="D33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="E33" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="27" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="I33" s="27" t="s">
+      <c r="I33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="27" t="s">
+      <c r="J33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="K33" s="27" t="s">
+      <c r="K33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="L33" s="27" t="s">
+      <c r="L33" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="M33" s="27" t="s">
+      <c r="M33" s="28" t="s">
         <v>100</v>
       </c>
+      <c r="N33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="26" t="s">
         <v>101</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -3844,10 +3880,10 @@
       <c r="D34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F34" s="26" t="s">
+      <c r="F34" s="27" t="s">
         <v>103</v>
       </c>
       <c r="G34" s="10" t="n">
@@ -3868,9 +3904,10 @@
       <c r="M34" s="10" t="n">
         <v>1E-006</v>
       </c>
+      <c r="N34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="26" t="s">
         <v>104</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -3882,10 +3919,10 @@
       <c r="D35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="E35" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="27" t="s">
         <v>103</v>
       </c>
       <c r="G35" s="10" t="n">
@@ -3906,9 +3943,10 @@
       <c r="M35" s="10" t="n">
         <v>0.001</v>
       </c>
+      <c r="N35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="26" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -3920,10 +3958,10 @@
       <c r="D36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="E36" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F36" s="26" t="s">
+      <c r="F36" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G36" s="10" t="s">
@@ -3944,9 +3982,10 @@
       <c r="M36" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="26" t="s">
         <v>108</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -3958,10 +3997,10 @@
       <c r="D37" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="E37" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="F37" s="26" t="s">
+      <c r="F37" s="27" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="10" t="s">
@@ -3982,9 +4021,10 @@
       <c r="M37" s="10" t="s">
         <v>110</v>
       </c>
+      <c r="N37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="26" t="s">
         <v>111</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -3996,10 +4036,10 @@
       <c r="D38" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G38" s="10" t="s">
@@ -4020,9 +4060,10 @@
       <c r="M38" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="26" t="s">
         <v>113</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -4034,10 +4075,10 @@
       <c r="D39" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G39" s="10" t="s">
@@ -4058,9 +4099,10 @@
       <c r="M39" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="26" t="s">
         <v>115</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -4072,10 +4114,10 @@
       <c r="D40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="E40" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="26" t="s">
+      <c r="F40" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G40" s="10" t="n">
@@ -4096,9 +4138,10 @@
       <c r="M40" s="10" t="n">
         <v>120</v>
       </c>
+      <c r="N40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="26" t="s">
         <v>117</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -4110,10 +4153,10 @@
       <c r="D41" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E41" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="F41" s="26" t="s">
+      <c r="F41" s="27" t="s">
         <v>119</v>
       </c>
       <c r="G41" s="10" t="n">
@@ -4134,9 +4177,10 @@
       <c r="M41" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="26" t="s">
         <v>120</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -4148,10 +4192,10 @@
       <c r="D42" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="E42" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="27" t="s">
         <v>119</v>
       </c>
       <c r="G42" s="10" t="n">
@@ -4172,9 +4216,10 @@
       <c r="M42" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="26" t="s">
         <v>122</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -4186,10 +4231,10 @@
       <c r="D43" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="E43" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="F43" s="26" t="s">
+      <c r="F43" s="27" t="s">
         <v>119</v>
       </c>
       <c r="G43" s="10" t="n">
@@ -4210,9 +4255,10 @@
       <c r="M43" s="10" t="n">
         <v>-0.1</v>
       </c>
+      <c r="N43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="26" t="s">
         <v>124</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -4224,10 +4270,10 @@
       <c r="D44" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="E44" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="F44" s="26" t="s">
+      <c r="F44" s="27" t="s">
         <v>119</v>
       </c>
       <c r="G44" s="10" t="n">
@@ -4248,9 +4294,10 @@
       <c r="M44" s="10" t="n">
         <v>-0.2</v>
       </c>
+      <c r="N44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="26" t="s">
         <v>126</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -4262,10 +4309,10 @@
       <c r="D45" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E45" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="F45" s="26" t="s">
+      <c r="F45" s="27" t="s">
         <v>119</v>
       </c>
       <c r="G45" s="10" t="n">
@@ -4286,9 +4333,10 @@
       <c r="M45" s="10" t="n">
         <v>0.4</v>
       </c>
+      <c r="N45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="26" t="s">
         <v>128</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -4300,10 +4348,10 @@
       <c r="D46" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E46" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="26" t="s">
+      <c r="F46" s="27" t="s">
         <v>130</v>
       </c>
       <c r="G46" s="10" t="n">
@@ -4324,9 +4372,10 @@
       <c r="M46" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="26" t="s">
         <v>131</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -4338,10 +4387,10 @@
       <c r="D47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="E47" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="26" t="s">
+      <c r="F47" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G47" s="10" t="n">
@@ -4362,9 +4411,10 @@
       <c r="M47" s="10" t="n">
         <v>1200</v>
       </c>
+      <c r="N47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="26" t="s">
         <v>133</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -4376,10 +4426,10 @@
       <c r="D48" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="E48" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="F48" s="26" t="s">
+      <c r="F48" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G48" s="10" t="n">
@@ -4400,9 +4450,10 @@
       <c r="M48" s="10" t="n">
         <v>1200</v>
       </c>
+      <c r="N48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>135</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -4414,10 +4465,10 @@
       <c r="D49" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="E49" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="F49" s="26" t="s">
+      <c r="F49" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G49" s="10" t="s">
@@ -4438,9 +4489,10 @@
       <c r="M49" s="10" t="s">
         <v>138</v>
       </c>
+      <c r="N49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="26" t="s">
         <v>139</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -4452,10 +4504,10 @@
       <c r="D50" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E50" s="26" t="s">
+      <c r="E50" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="F50" s="26" t="s">
+      <c r="F50" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G50" s="10" t="s">
@@ -4476,9 +4528,10 @@
       <c r="M50" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="29" t="s">
         <v>141</v>
       </c>
       <c r="B51" s="8" t="s">
@@ -4490,10 +4543,10 @@
       <c r="D51" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="29" t="s">
+      <c r="E51" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="F51" s="29" t="s">
+      <c r="F51" s="30" t="s">
         <v>35</v>
       </c>
       <c r="G51" s="10" t="s">
@@ -4514,9 +4567,10 @@
       <c r="M51" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N51" s="11"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>143</v>
       </c>
       <c r="B52" s="8" t="s">
@@ -4528,10 +4582,10 @@
       <c r="D52" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="29" t="s">
+      <c r="E52" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="F52" s="29" t="s">
+      <c r="F52" s="30" t="s">
         <v>119</v>
       </c>
       <c r="G52" s="10" t="n">
@@ -4552,9 +4606,10 @@
       <c r="M52" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="29" t="s">
         <v>145</v>
       </c>
       <c r="B53" s="8" t="s">
@@ -4566,10 +4621,10 @@
       <c r="D53" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="29" t="s">
+      <c r="E53" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="F53" s="29" t="s">
+      <c r="F53" s="30" t="s">
         <v>119</v>
       </c>
       <c r="G53" s="10" t="n">
@@ -4590,9 +4645,10 @@
       <c r="M53" s="10" t="n">
         <v>0.5</v>
       </c>
+      <c r="N53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="29" t="s">
         <v>147</v>
       </c>
       <c r="B54" s="8" t="s">
@@ -4604,10 +4660,10 @@
       <c r="D54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="29" t="s">
+      <c r="E54" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="F54" s="29" t="s">
+      <c r="F54" s="30" t="s">
         <v>119</v>
       </c>
       <c r="G54" s="10" t="n">
@@ -4628,9 +4684,10 @@
       <c r="M54" s="10" t="n">
         <v>0.05</v>
       </c>
+      <c r="N54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="31" t="s">
         <v>149</v>
       </c>
       <c r="B55" s="8" t="s">
@@ -4642,10 +4699,10 @@
       <c r="D55" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E55" s="31" t="s">
+      <c r="E55" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="F55" s="31" t="s">
+      <c r="F55" s="32" t="s">
         <v>119</v>
       </c>
       <c r="G55" s="10" t="n">
@@ -4666,9 +4723,10 @@
       <c r="M55" s="10" t="n">
         <v>0.001</v>
       </c>
+      <c r="N55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>151</v>
       </c>
       <c r="B56" s="8" t="s">
@@ -4680,10 +4738,10 @@
       <c r="D56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="F56" s="31" t="s">
+      <c r="F56" s="32" t="s">
         <v>119</v>
       </c>
       <c r="G56" s="10" t="n">
@@ -4704,9 +4762,10 @@
       <c r="M56" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="31" t="s">
         <v>153</v>
       </c>
       <c r="B57" s="8" t="s">
@@ -4718,10 +4777,10 @@
       <c r="D57" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="32" t="s">
         <v>155</v>
       </c>
       <c r="G57" s="10" t="n">
@@ -4742,9 +4801,10 @@
       <c r="M57" s="10" t="n">
         <v>0.0001</v>
       </c>
+      <c r="N57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="31" t="s">
         <v>156</v>
       </c>
       <c r="B58" s="8" t="s">
@@ -4756,10 +4816,10 @@
       <c r="D58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E58" s="31" t="s">
+      <c r="E58" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="F58" s="31" t="s">
+      <c r="F58" s="32" t="s">
         <v>155</v>
       </c>
       <c r="G58" s="10" t="n">
@@ -4780,9 +4840,10 @@
       <c r="M58" s="10" t="n">
         <v>0.0001</v>
       </c>
+      <c r="N58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="33" t="s">
         <v>158</v>
       </c>
       <c r="B59" s="8" t="s">
@@ -4794,10 +4855,10 @@
       <c r="D59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E59" s="33" t="s">
+      <c r="E59" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="F59" s="33" t="s">
+      <c r="F59" s="34" t="s">
         <v>119</v>
       </c>
       <c r="G59" s="10" t="n">
@@ -4818,9 +4879,10 @@
       <c r="M59" s="10" t="n">
         <v>0.0007</v>
       </c>
+      <c r="N59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="32" t="s">
+      <c r="A60" s="33" t="s">
         <v>160</v>
       </c>
       <c r="B60" s="8" t="s">
@@ -4832,10 +4894,10 @@
       <c r="D60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="33" t="s">
+      <c r="E60" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="F60" s="33" t="s">
+      <c r="F60" s="34" t="s">
         <v>119</v>
       </c>
       <c r="G60" s="10" t="n">
@@ -4856,9 +4918,10 @@
       <c r="M60" s="10" t="n">
         <v>0.000122</v>
       </c>
+      <c r="N60" s="11"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="32" t="s">
+      <c r="A61" s="33" t="s">
         <v>162</v>
       </c>
       <c r="B61" s="8" t="s">
@@ -4870,10 +4933,10 @@
       <c r="D61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E61" s="33" t="s">
+      <c r="E61" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="F61" s="33" t="s">
+      <c r="F61" s="34" t="s">
         <v>119</v>
       </c>
       <c r="G61" s="10" t="n">
@@ -4894,9 +4957,10 @@
       <c r="M61" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="32" t="s">
+      <c r="A62" s="33" t="s">
         <v>164</v>
       </c>
       <c r="B62" s="8" t="s">
@@ -4908,10 +4972,10 @@
       <c r="D62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="33" t="s">
+      <c r="E62" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="F62" s="33" t="s">
+      <c r="F62" s="34" t="s">
         <v>166</v>
       </c>
       <c r="G62" s="10" t="n">
@@ -4932,9 +4996,10 @@
       <c r="M62" s="10" t="n">
         <v>0.95</v>
       </c>
+      <c r="N62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="33" t="s">
         <v>167</v>
       </c>
       <c r="B63" s="8" t="s">
@@ -4946,10 +5011,10 @@
       <c r="D63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E63" s="33" t="s">
+      <c r="E63" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="F63" s="33" t="s">
+      <c r="F63" s="34" t="s">
         <v>35</v>
       </c>
       <c r="G63" s="10" t="s">
@@ -4970,9 +5035,10 @@
       <c r="M63" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="33" t="s">
         <v>169</v>
       </c>
       <c r="B64" s="8" t="s">
@@ -4984,10 +5050,10 @@
       <c r="D64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E64" s="33" t="s">
+      <c r="E64" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="F64" s="33" t="s">
+      <c r="F64" s="34" t="s">
         <v>171</v>
       </c>
       <c r="G64" s="10" t="n">
@@ -5008,9 +5074,10 @@
       <c r="M64" s="10" t="n">
         <v>5</v>
       </c>
+      <c r="N64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="32" t="s">
+      <c r="A65" s="33" t="s">
         <v>172</v>
       </c>
       <c r="B65" s="8" t="s">
@@ -5022,10 +5089,10 @@
       <c r="D65" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="33" t="s">
+      <c r="E65" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="F65" s="33" t="s">
+      <c r="F65" s="34" t="s">
         <v>35</v>
       </c>
       <c r="G65" s="10" t="s">
@@ -5046,9 +5113,10 @@
       <c r="M65" s="10" t="s">
         <v>53</v>
       </c>
+      <c r="N65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="33" t="s">
         <v>174</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -5060,10 +5128,10 @@
       <c r="D66" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E66" s="33" t="s">
+      <c r="E66" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="F66" s="33" t="s">
+      <c r="F66" s="34" t="s">
         <v>171</v>
       </c>
       <c r="G66" s="10" t="n">
@@ -5084,9 +5152,10 @@
       <c r="M66" s="10" t="n">
         <v>50</v>
       </c>
+      <c r="N66" s="11"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="32" t="s">
+      <c r="A67" s="33" t="s">
         <v>176</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -5098,10 +5167,10 @@
       <c r="D67" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E67" s="33" t="s">
+      <c r="E67" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="F67" s="34" t="s">
         <v>178</v>
       </c>
       <c r="G67" s="10" t="n">
@@ -5122,9 +5191,10 @@
       <c r="M67" s="10" t="n">
         <v>1453890.89418848</v>
       </c>
+      <c r="N67" s="11"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="33" t="s">
         <v>179</v>
       </c>
       <c r="B68" s="8" t="s">
@@ -5136,10 +5206,10 @@
       <c r="D68" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E68" s="33" t="s">
+      <c r="E68" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F68" s="34" t="s">
         <v>181</v>
       </c>
       <c r="G68" s="10" t="n">
@@ -5160,9 +5230,10 @@
       <c r="M68" s="10" t="n">
         <v>1.38888888888889E-005</v>
       </c>
+      <c r="N68" s="11"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="33" t="s">
         <v>182</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -5174,10 +5245,10 @@
       <c r="D69" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="33" t="s">
+      <c r="E69" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="F69" s="33" t="s">
+      <c r="F69" s="34" t="s">
         <v>184</v>
       </c>
       <c r="G69" s="10" t="n">
@@ -5198,9 +5269,10 @@
       <c r="M69" s="10" t="n">
         <v>0.000650115740740741</v>
       </c>
+      <c r="N69" s="11"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="33" t="s">
         <v>185</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -5212,10 +5284,10 @@
       <c r="D70" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="33" t="s">
+      <c r="E70" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="F70" s="33" t="s">
+      <c r="F70" s="34" t="s">
         <v>119</v>
       </c>
       <c r="G70" s="10" t="n">
@@ -5236,9 +5308,10 @@
       <c r="M70" s="10" t="n">
         <v>0.00474</v>
       </c>
+      <c r="N70" s="11"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="33" t="s">
         <v>187</v>
       </c>
       <c r="B71" s="8" t="s">
@@ -5250,10 +5323,10 @@
       <c r="D71" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E71" s="33" t="s">
+      <c r="E71" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="34" t="s">
         <v>178</v>
       </c>
       <c r="G71" s="10" t="n">
@@ -5274,9 +5347,10 @@
       <c r="M71" s="10" t="n">
         <v>282528</v>
       </c>
+      <c r="N71" s="11"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="32" t="s">
+      <c r="A72" s="33" t="s">
         <v>189</v>
       </c>
       <c r="B72" s="8" t="s">
@@ -5288,10 +5362,10 @@
       <c r="D72" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E72" s="33" t="s">
+      <c r="E72" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="F72" s="33" t="s">
+      <c r="F72" s="34" t="s">
         <v>166</v>
       </c>
       <c r="G72" s="10" t="n">
@@ -5312,9 +5386,10 @@
       <c r="M72" s="10" t="n">
         <v>0.57</v>
       </c>
+      <c r="N72" s="11"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="32" t="s">
+      <c r="A73" s="33" t="s">
         <v>191</v>
       </c>
       <c r="B73" s="8" t="s">
@@ -5326,10 +5401,10 @@
       <c r="D73" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E73" s="33" t="s">
+      <c r="E73" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="F73" s="33" t="s">
+      <c r="F73" s="34" t="s">
         <v>193</v>
       </c>
       <c r="G73" s="10" t="n">
@@ -5350,9 +5425,10 @@
       <c r="M73" s="10" t="n">
         <v>0.16</v>
       </c>
+      <c r="N73" s="11"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="32" t="s">
+      <c r="A74" s="33" t="s">
         <v>194</v>
       </c>
       <c r="B74" s="8" t="s">
@@ -5364,10 +5440,10 @@
       <c r="D74" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="F74" s="33" t="s">
+      <c r="F74" s="34" t="s">
         <v>196</v>
       </c>
       <c r="G74" s="10" t="n">
@@ -5388,9 +5464,10 @@
       <c r="M74" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N74" s="11"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="34" t="s">
+      <c r="A75" s="35" t="s">
         <v>197</v>
       </c>
       <c r="B75" s="8" t="s">
@@ -5402,10 +5479,10 @@
       <c r="D75" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="35" t="s">
+      <c r="E75" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="36" t="s">
         <v>199</v>
       </c>
       <c r="G75" s="10" t="n">
@@ -5426,9 +5503,10 @@
       <c r="M75" s="10" t="n">
         <v>745476480000</v>
       </c>
+      <c r="N75" s="11"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="34" t="s">
+      <c r="A76" s="35" t="s">
         <v>200</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -5440,10 +5518,10 @@
       <c r="D76" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E76" s="35" t="s">
+      <c r="E76" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="F76" s="35" t="s">
+      <c r="F76" s="36" t="s">
         <v>202</v>
       </c>
       <c r="G76" s="10" t="n">
@@ -5464,9 +5542,10 @@
       <c r="M76" s="10" t="n">
         <v>100</v>
       </c>
+      <c r="N76" s="11"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="34" t="s">
+      <c r="A77" s="35" t="s">
         <v>203</v>
       </c>
       <c r="B77" s="8" t="s">
@@ -5478,10 +5557,10 @@
       <c r="D77" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="35" t="s">
+      <c r="E77" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="F77" s="35" t="s">
+      <c r="F77" s="36" t="s">
         <v>35</v>
       </c>
       <c r="G77" s="10" t="s">
@@ -5502,9 +5581,10 @@
       <c r="M77" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N77" s="11"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="34" t="s">
+      <c r="A78" s="35" t="s">
         <v>205</v>
       </c>
       <c r="B78" s="8" t="s">
@@ -5516,10 +5596,10 @@
       <c r="D78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E78" s="35" t="s">
+      <c r="E78" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="F78" s="35" t="s">
+      <c r="F78" s="36" t="s">
         <v>178</v>
       </c>
       <c r="G78" s="10" t="n">
@@ -5540,9 +5620,10 @@
       <c r="M78" s="10" t="n">
         <v>21600</v>
       </c>
+      <c r="N78" s="11"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="34" t="s">
+      <c r="A79" s="35" t="s">
         <v>207</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -5554,10 +5635,10 @@
       <c r="D79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E79" s="35" t="s">
+      <c r="E79" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="F79" s="35" t="s">
+      <c r="F79" s="36" t="s">
         <v>193</v>
       </c>
       <c r="G79" s="10" t="n">
@@ -5578,9 +5659,10 @@
       <c r="M79" s="10" t="n">
         <v>0.5</v>
       </c>
+      <c r="N79" s="11"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="34" t="s">
+      <c r="A80" s="35" t="s">
         <v>209</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -5592,10 +5674,10 @@
       <c r="D80" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="35" t="s">
+      <c r="E80" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="36" t="s">
         <v>178</v>
       </c>
       <c r="G80" s="10" t="n">
@@ -5616,9 +5698,10 @@
       <c r="M80" s="10" t="n">
         <v>60480</v>
       </c>
+      <c r="N80" s="11"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="34" t="s">
+      <c r="A81" s="35" t="s">
         <v>211</v>
       </c>
       <c r="B81" s="8" t="s">
@@ -5630,10 +5713,10 @@
       <c r="D81" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E81" s="35" t="s">
+      <c r="E81" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="36" t="s">
         <v>193</v>
       </c>
       <c r="G81" s="10" t="n">
@@ -5654,9 +5737,10 @@
       <c r="M81" s="10" t="n">
         <v>0.85</v>
       </c>
+      <c r="N81" s="11"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="34" t="s">
+      <c r="A82" s="35" t="s">
         <v>213</v>
       </c>
       <c r="B82" s="8" t="s">
@@ -5668,10 +5752,10 @@
       <c r="D82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E82" s="35" t="s">
+      <c r="E82" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="36" t="s">
         <v>178</v>
       </c>
       <c r="G82" s="10" t="n">
@@ -5692,9 +5776,10 @@
       <c r="M82" s="10" t="n">
         <v>518400</v>
       </c>
+      <c r="N82" s="11"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="34" t="s">
+      <c r="A83" s="35" t="s">
         <v>215</v>
       </c>
       <c r="B83" s="8" t="s">
@@ -5706,10 +5791,10 @@
       <c r="D83" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E83" s="35" t="s">
+      <c r="E83" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="36" t="s">
         <v>178</v>
       </c>
       <c r="G83" s="10" t="n">
@@ -5730,9 +5815,10 @@
       <c r="M83" s="10" t="n">
         <v>5184000</v>
       </c>
+      <c r="N83" s="11"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="32" t="s">
+      <c r="A84" s="33" t="s">
         <v>217</v>
       </c>
       <c r="B84" s="8" t="s">
@@ -5744,10 +5830,10 @@
       <c r="D84" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="33" t="s">
+      <c r="E84" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="F84" s="33" t="s">
+      <c r="F84" s="34" t="s">
         <v>219</v>
       </c>
       <c r="G84" s="10" t="n">
@@ -5768,9 +5854,10 @@
       <c r="M84" s="10" t="n">
         <v>50000</v>
       </c>
+      <c r="N84" s="11"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="33" t="s">
         <v>220</v>
       </c>
       <c r="B85" s="8" t="s">
@@ -5782,10 +5869,10 @@
       <c r="D85" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E85" s="33" t="s">
+      <c r="E85" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="F85" s="33" t="s">
+      <c r="F85" s="34" t="s">
         <v>222</v>
       </c>
       <c r="G85" s="10" t="n">
@@ -5806,9 +5893,10 @@
       <c r="M85" s="10" t="n">
         <v>140000</v>
       </c>
+      <c r="N85" s="11"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="32" t="s">
+      <c r="A86" s="33" t="s">
         <v>223</v>
       </c>
       <c r="B86" s="8" t="s">
@@ -5820,10 +5908,10 @@
       <c r="D86" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E86" s="33" t="s">
+      <c r="E86" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="F86" s="33" t="s">
+      <c r="F86" s="34" t="s">
         <v>225</v>
       </c>
       <c r="G86" s="10" t="n">
@@ -5844,9 +5932,10 @@
       <c r="M86" s="10" t="n">
         <v>0.036636137</v>
       </c>
+      <c r="N86" s="11"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="32" t="s">
+      <c r="A87" s="33" t="s">
         <v>226</v>
       </c>
       <c r="B87" s="8" t="s">
@@ -5858,10 +5947,10 @@
       <c r="D87" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E87" s="33" t="s">
+      <c r="E87" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="F87" s="33" t="s">
+      <c r="F87" s="34" t="s">
         <v>119</v>
       </c>
       <c r="G87" s="10" t="n">
@@ -5882,9 +5971,10 @@
       <c r="M87" s="10" t="n">
         <v>0.0045</v>
       </c>
+      <c r="N87" s="11"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="32" t="s">
+      <c r="A88" s="33" t="s">
         <v>228</v>
       </c>
       <c r="B88" s="8" t="s">
@@ -5896,10 +5986,10 @@
       <c r="D88" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E88" s="33" t="s">
+      <c r="E88" s="34" t="s">
         <v>229</v>
       </c>
-      <c r="F88" s="33" t="s">
+      <c r="F88" s="34" t="s">
         <v>193</v>
       </c>
       <c r="G88" s="10" t="n">
@@ -5920,9 +6010,10 @@
       <c r="M88" s="10" t="n">
         <v>0.05</v>
       </c>
+      <c r="N88" s="11"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="36" t="s">
+      <c r="A89" s="37" t="s">
         <v>230</v>
       </c>
       <c r="B89" s="8" t="s">
@@ -5934,10 +6025,10 @@
       <c r="D89" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E89" s="37" t="s">
+      <c r="E89" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="F89" s="37" t="s">
+      <c r="F89" s="38" t="s">
         <v>119</v>
       </c>
       <c r="G89" s="10" t="n">
@@ -5958,9 +6049,10 @@
       <c r="M89" s="10" t="n">
         <v>6E-006</v>
       </c>
+      <c r="N89" s="11"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="36" t="s">
+      <c r="A90" s="37" t="s">
         <v>232</v>
       </c>
       <c r="B90" s="8" t="s">
@@ -5972,10 +6064,10 @@
       <c r="D90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E90" s="37" t="s">
+      <c r="E90" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="F90" s="37" t="s">
+      <c r="F90" s="38" t="s">
         <v>119</v>
       </c>
       <c r="G90" s="10" t="n">
@@ -5996,9 +6088,10 @@
       <c r="M90" s="10" t="n">
         <v>0.001</v>
       </c>
+      <c r="N90" s="11"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="36" t="s">
+      <c r="A91" s="37" t="s">
         <v>234</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -6010,10 +6103,10 @@
       <c r="D91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E91" s="37" t="s">
+      <c r="E91" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="F91" s="37" t="s">
+      <c r="F91" s="38" t="s">
         <v>236</v>
       </c>
       <c r="G91" s="10" t="n">
@@ -6034,9 +6127,10 @@
       <c r="M91" s="10" t="n">
         <v>375000000</v>
       </c>
+      <c r="N91" s="11"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="36" t="s">
+      <c r="A92" s="37" t="s">
         <v>237</v>
       </c>
       <c r="B92" s="8" t="s">
@@ -6048,10 +6142,10 @@
       <c r="D92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E92" s="37" t="s">
+      <c r="E92" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="F92" s="37" t="s">
+      <c r="F92" s="38" t="s">
         <v>239</v>
       </c>
       <c r="G92" s="10" t="n">
@@ -6072,9 +6166,10 @@
       <c r="M92" s="10" t="n">
         <v>0.0037037037037037</v>
       </c>
+      <c r="N92" s="11"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="36" t="s">
+      <c r="A93" s="37" t="s">
         <v>240</v>
       </c>
       <c r="B93" s="8" t="s">
@@ -6086,10 +6181,10 @@
       <c r="D93" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E93" s="37" t="s">
+      <c r="E93" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="F93" s="37" t="s">
+      <c r="F93" s="38" t="s">
         <v>68</v>
       </c>
       <c r="G93" s="10" t="n">
@@ -6110,9 +6205,10 @@
       <c r="M93" s="10" t="n">
         <v>165600</v>
       </c>
+      <c r="N93" s="11"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="26" t="s">
         <v>242</v>
       </c>
       <c r="B94" s="8" t="s">
@@ -6124,10 +6220,10 @@
       <c r="D94" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E94" s="26" t="s">
+      <c r="E94" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="F94" s="26" t="s">
+      <c r="F94" s="27" t="s">
         <v>244</v>
       </c>
       <c r="G94" s="10" t="n">
@@ -6148,9 +6244,10 @@
       <c r="M94" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N94" s="11"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="25" t="s">
+      <c r="A95" s="26" t="s">
         <v>245</v>
       </c>
       <c r="B95" s="8" t="s">
@@ -6162,10 +6259,10 @@
       <c r="D95" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="26" t="s">
+      <c r="E95" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="F95" s="26" t="s">
+      <c r="F95" s="27" t="s">
         <v>193</v>
       </c>
       <c r="G95" s="10" t="n">
@@ -6186,9 +6283,10 @@
       <c r="M95" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N95" s="11"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="25" t="s">
+      <c r="A96" s="26" t="s">
         <v>247</v>
       </c>
       <c r="B96" s="8" t="s">
@@ -6200,10 +6298,10 @@
       <c r="D96" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E96" s="26" t="s">
+      <c r="E96" s="27" t="s">
         <v>248</v>
       </c>
-      <c r="F96" s="26" t="s">
+      <c r="F96" s="27" t="s">
         <v>166</v>
       </c>
       <c r="G96" s="10" t="n">
@@ -6224,9 +6322,10 @@
       <c r="M96" s="10" t="n">
         <v>21</v>
       </c>
+      <c r="N96" s="11"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="38" t="s">
+      <c r="A97" s="39" t="s">
         <v>249</v>
       </c>
       <c r="B97" s="8" t="s">
@@ -6238,10 +6337,10 @@
       <c r="D97" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E97" s="39" t="s">
+      <c r="E97" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F97" s="39" t="s">
+      <c r="F97" s="40" t="s">
         <v>251</v>
       </c>
       <c r="G97" s="10" t="n">
@@ -6262,9 +6361,10 @@
       <c r="M97" s="10" t="n">
         <v>0.64</v>
       </c>
+      <c r="N97" s="11"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="38" t="s">
+      <c r="A98" s="39" t="s">
         <v>252</v>
       </c>
       <c r="B98" s="8" t="s">
@@ -6276,10 +6376,10 @@
       <c r="D98" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E98" s="39" t="s">
+      <c r="E98" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="F98" s="39" t="s">
+      <c r="F98" s="40" t="s">
         <v>251</v>
       </c>
       <c r="G98" s="10" t="n">
@@ -6300,9 +6400,10 @@
       <c r="M98" s="10" t="n">
         <v>8</v>
       </c>
+      <c r="N98" s="11"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="38" t="s">
+      <c r="A99" s="39" t="s">
         <v>254</v>
       </c>
       <c r="B99" s="8" t="s">
@@ -6314,10 +6415,10 @@
       <c r="D99" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E99" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="F99" s="39" t="s">
+      <c r="F99" s="40" t="s">
         <v>251</v>
       </c>
       <c r="G99" s="10" t="n">
@@ -6338,9 +6439,10 @@
       <c r="M99" s="10" t="n">
         <v>10</v>
       </c>
+      <c r="N99" s="11"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="38" t="s">
+      <c r="A100" s="39" t="s">
         <v>256</v>
       </c>
       <c r="B100" s="8" t="s">
@@ -6352,10 +6454,10 @@
       <c r="D100" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E100" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="F100" s="39" t="s">
+      <c r="F100" s="40" t="s">
         <v>251</v>
       </c>
       <c r="G100" s="10" t="n">
@@ -6376,9 +6478,10 @@
       <c r="M100" s="10" t="n">
         <v>8</v>
       </c>
+      <c r="N100" s="11"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="38" t="s">
+      <c r="A101" s="39" t="s">
         <v>258</v>
       </c>
       <c r="B101" s="8" t="s">
@@ -6390,10 +6493,10 @@
       <c r="D101" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E101" s="39" t="s">
+      <c r="E101" s="40" t="s">
         <v>259</v>
       </c>
-      <c r="F101" s="39" t="s">
+      <c r="F101" s="40" t="s">
         <v>166</v>
       </c>
       <c r="G101" s="10" t="n">
@@ -6414,9 +6517,10 @@
       <c r="M101" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N101" s="11"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="38" t="s">
+      <c r="A102" s="39" t="s">
         <v>260</v>
       </c>
       <c r="B102" s="8" t="s">
@@ -6428,10 +6532,10 @@
       <c r="D102" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E102" s="39" t="s">
+      <c r="E102" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="F102" s="39" t="s">
+      <c r="F102" s="40" t="s">
         <v>262</v>
       </c>
       <c r="G102" s="10" t="n">
@@ -6452,9 +6556,10 @@
       <c r="M102" s="10" t="n">
         <v>0.5</v>
       </c>
+      <c r="N102" s="11"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="39" t="s">
         <v>263</v>
       </c>
       <c r="B103" s="8" t="s">
@@ -6466,10 +6571,10 @@
       <c r="D103" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E103" s="39" t="s">
+      <c r="E103" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="F103" s="39" t="s">
+      <c r="F103" s="40" t="s">
         <v>265</v>
       </c>
       <c r="G103" s="10" t="n">
@@ -6496,9 +6601,10 @@
         <f aca="false">10/0.1</f>
         <v>100</v>
       </c>
+      <c r="N103" s="11"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="38" t="s">
+      <c r="A104" s="39" t="s">
         <v>266</v>
       </c>
       <c r="B104" s="8" t="s">
@@ -6510,10 +6616,10 @@
       <c r="D104" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="39" t="s">
+      <c r="E104" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="F104" s="39" t="s">
+      <c r="F104" s="40" t="s">
         <v>265</v>
       </c>
       <c r="G104" s="10" t="n">
@@ -6540,9 +6646,10 @@
         <f aca="false">150/0.1</f>
         <v>1500</v>
       </c>
+      <c r="N104" s="11"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="38" t="s">
+      <c r="A105" s="39" t="s">
         <v>267</v>
       </c>
       <c r="B105" s="8" t="s">
@@ -6554,10 +6661,10 @@
       <c r="D105" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="39" t="s">
+      <c r="E105" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="F105" s="39" t="s">
+      <c r="F105" s="40" t="s">
         <v>265</v>
       </c>
       <c r="G105" s="10" t="n">
@@ -6584,9 +6691,10 @@
         <f aca="false">20/0.1</f>
         <v>200</v>
       </c>
+      <c r="N105" s="11"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="38" t="s">
+      <c r="A106" s="39" t="s">
         <v>268</v>
       </c>
       <c r="B106" s="8" t="s">
@@ -6598,10 +6706,10 @@
       <c r="D106" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="39" t="s">
+      <c r="E106" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="F106" s="39" t="s">
+      <c r="F106" s="40" t="s">
         <v>265</v>
       </c>
       <c r="G106" s="10" t="n">
@@ -6628,9 +6736,10 @@
         <f aca="false">400/0.1</f>
         <v>4000</v>
       </c>
+      <c r="N106" s="11"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="38" t="s">
+      <c r="A107" s="39" t="s">
         <v>269</v>
       </c>
       <c r="B107" s="8" t="s">
@@ -6642,10 +6751,10 @@
       <c r="D107" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E107" s="39" t="s">
+      <c r="E107" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="F107" s="39" t="s">
+      <c r="F107" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G107" s="10" t="n">
@@ -6671,9 +6780,10 @@
         <f aca="false">10/0.1</f>
         <v>100</v>
       </c>
+      <c r="N107" s="11"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="38" t="s">
+      <c r="A108" s="39" t="s">
         <v>271</v>
       </c>
       <c r="B108" s="8" t="s">
@@ -6685,10 +6795,10 @@
       <c r="D108" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E108" s="39" t="s">
+      <c r="E108" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="F108" s="39" t="s">
+      <c r="F108" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G108" s="10" t="n">
@@ -6714,9 +6824,10 @@
         <f aca="false">150/0.1</f>
         <v>1500</v>
       </c>
+      <c r="N108" s="11"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="38" t="s">
+      <c r="A109" s="39" t="s">
         <v>273</v>
       </c>
       <c r="B109" s="8" t="s">
@@ -6728,10 +6839,10 @@
       <c r="D109" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E109" s="39" t="s">
+      <c r="E109" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="F109" s="39" t="s">
+      <c r="F109" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G109" s="10" t="n">
@@ -6757,9 +6868,10 @@
         <f aca="false">20/0.1</f>
         <v>200</v>
       </c>
+      <c r="N109" s="11"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="38" t="s">
+      <c r="A110" s="39" t="s">
         <v>275</v>
       </c>
       <c r="B110" s="8" t="s">
@@ -6771,10 +6883,10 @@
       <c r="D110" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="39" t="s">
+      <c r="E110" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="F110" s="39" t="s">
+      <c r="F110" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G110" s="10" t="n">
@@ -6800,9 +6912,10 @@
         <f aca="false">400/0.1</f>
         <v>4000</v>
       </c>
+      <c r="N110" s="11"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="38" t="s">
+      <c r="A111" s="39" t="s">
         <v>277</v>
       </c>
       <c r="B111" s="8" t="s">
@@ -6814,10 +6927,10 @@
       <c r="D111" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="39" t="s">
+      <c r="E111" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="F111" s="39" t="s">
+      <c r="F111" s="40" t="s">
         <v>279</v>
       </c>
       <c r="G111" s="10" t="n">
@@ -6838,9 +6951,10 @@
       <c r="M111" s="10" t="n">
         <v>100</v>
       </c>
+      <c r="N111" s="11"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="38" t="s">
+      <c r="A112" s="39" t="s">
         <v>280</v>
       </c>
       <c r="B112" s="8" t="s">
@@ -6852,10 +6966,10 @@
       <c r="D112" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E112" s="39" t="s">
+      <c r="E112" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="F112" s="39" t="s">
+      <c r="F112" s="40" t="s">
         <v>282</v>
       </c>
       <c r="G112" s="10" t="n">
@@ -6876,9 +6990,10 @@
       <c r="M112" s="10" t="n">
         <v>280800</v>
       </c>
+      <c r="N112" s="11"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="38" t="s">
+      <c r="A113" s="39" t="s">
         <v>283</v>
       </c>
       <c r="B113" s="8" t="s">
@@ -6890,10 +7005,10 @@
       <c r="D113" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E113" s="39" t="s">
+      <c r="E113" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="F113" s="39" t="s">
+      <c r="F113" s="40" t="s">
         <v>285</v>
       </c>
       <c r="G113" s="10" t="n">
@@ -6919,9 +7034,10 @@
         <f aca="false">1.11 / 10</f>
         <v>0.111</v>
       </c>
+      <c r="N113" s="11"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="38" t="s">
+      <c r="A114" s="39" t="s">
         <v>286</v>
       </c>
       <c r="B114" s="8" t="s">
@@ -6933,10 +7049,10 @@
       <c r="D114" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E114" s="39" t="s">
+      <c r="E114" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="F114" s="39" t="s">
+      <c r="F114" s="40" t="s">
         <v>279</v>
       </c>
       <c r="G114" s="10" t="n">
@@ -6957,9 +7073,10 @@
       <c r="M114" s="10" t="n">
         <v>100</v>
       </c>
+      <c r="N114" s="11"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="38" t="s">
+      <c r="A115" s="39" t="s">
         <v>288</v>
       </c>
       <c r="B115" s="8" t="s">
@@ -6971,10 +7088,10 @@
       <c r="D115" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E115" s="39" t="s">
+      <c r="E115" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="F115" s="39" t="s">
+      <c r="F115" s="40" t="s">
         <v>282</v>
       </c>
       <c r="G115" s="10" t="n">
@@ -6995,9 +7112,10 @@
       <c r="M115" s="10" t="n">
         <v>459648</v>
       </c>
+      <c r="N115" s="11"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="38" t="s">
+      <c r="A116" s="39" t="s">
         <v>290</v>
       </c>
       <c r="B116" s="8" t="s">
@@ -7009,10 +7127,10 @@
       <c r="D116" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E116" s="39" t="s">
+      <c r="E116" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="F116" s="39" t="s">
+      <c r="F116" s="40" t="s">
         <v>285</v>
       </c>
       <c r="G116" s="10" t="n">
@@ -7038,9 +7156,10 @@
         <f aca="false">1.11/8</f>
         <v>0.13875</v>
       </c>
+      <c r="N116" s="11"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="38" t="s">
+      <c r="A117" s="39" t="s">
         <v>292</v>
       </c>
       <c r="B117" s="8" t="s">
@@ -7052,10 +7171,10 @@
       <c r="D117" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E117" s="39" t="s">
+      <c r="E117" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="F117" s="39" t="s">
+      <c r="F117" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G117" s="10" t="n">
@@ -7076,9 +7195,10 @@
       <c r="M117" s="10" t="n">
         <v>21600</v>
       </c>
+      <c r="N117" s="11"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="38" t="s">
+      <c r="A118" s="39" t="s">
         <v>294</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -7090,10 +7210,10 @@
       <c r="D118" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E118" s="39" t="s">
+      <c r="E118" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="F118" s="39" t="s">
+      <c r="F118" s="40" t="s">
         <v>178</v>
       </c>
       <c r="G118" s="10" t="n">
@@ -7114,9 +7234,10 @@
       <c r="M118" s="10" t="n">
         <v>43200</v>
       </c>
+      <c r="N118" s="11"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="25" t="s">
+      <c r="A119" s="26" t="s">
         <v>296</v>
       </c>
       <c r="B119" s="8" t="s">
@@ -7128,10 +7249,10 @@
       <c r="D119" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E119" s="26" t="s">
+      <c r="E119" s="27" t="s">
         <v>297</v>
       </c>
-      <c r="F119" s="26" t="s">
+      <c r="F119" s="27" t="s">
         <v>298</v>
       </c>
       <c r="G119" s="10" t="n">
@@ -7152,9 +7273,10 @@
       <c r="M119" s="10" t="n">
         <v>0.8</v>
       </c>
+      <c r="N119" s="11"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="25" t="s">
+      <c r="A120" s="26" t="s">
         <v>299</v>
       </c>
       <c r="B120" s="8" t="s">
@@ -7166,10 +7288,10 @@
       <c r="D120" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E120" s="26" t="s">
+      <c r="E120" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="F120" s="26" t="s">
+      <c r="F120" s="27" t="s">
         <v>301</v>
       </c>
       <c r="G120" s="10" t="n">
@@ -7195,9 +7317,10 @@
         <f aca="false">0.000208333333333333 / 2</f>
         <v>0.000104166666666667</v>
       </c>
+      <c r="N120" s="11"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="25" t="s">
+      <c r="A121" s="26" t="s">
         <v>302</v>
       </c>
       <c r="B121" s="8" t="s">
@@ -7209,10 +7332,10 @@
       <c r="D121" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E121" s="26" t="s">
+      <c r="E121" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="F121" s="26" t="s">
+      <c r="F121" s="27" t="s">
         <v>304</v>
       </c>
       <c r="G121" s="10" t="n">
@@ -7233,9 +7356,10 @@
       <c r="M121" s="10" t="n">
         <v>5.79E-007</v>
       </c>
+      <c r="N121" s="11"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="25" t="s">
+      <c r="A122" s="26" t="s">
         <v>305</v>
       </c>
       <c r="B122" s="8" t="s">
@@ -7247,10 +7371,10 @@
       <c r="D122" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E122" s="26" t="s">
+      <c r="E122" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="F122" s="26" t="s">
+      <c r="F122" s="27" t="s">
         <v>301</v>
       </c>
       <c r="G122" s="10" t="n">
@@ -7271,9 +7395,10 @@
       <c r="M122" s="10" t="n">
         <v>0.000208333333333333</v>
       </c>
+      <c r="N122" s="11"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="25" t="s">
+      <c r="A123" s="26" t="s">
         <v>307</v>
       </c>
       <c r="B123" s="8" t="s">
@@ -7285,10 +7410,10 @@
       <c r="D123" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E123" s="26" t="s">
+      <c r="E123" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="F123" s="26" t="s">
+      <c r="F123" s="27" t="s">
         <v>301</v>
       </c>
       <c r="G123" s="10" t="n">
@@ -7309,9 +7434,10 @@
       <c r="M123" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N123" s="11"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="25" t="s">
+      <c r="A124" s="26" t="s">
         <v>309</v>
       </c>
       <c r="B124" s="8" t="s">
@@ -7323,10 +7449,10 @@
       <c r="D124" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E124" s="26" t="s">
+      <c r="E124" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="F124" s="26" t="s">
+      <c r="F124" s="27" t="s">
         <v>301</v>
       </c>
       <c r="G124" s="10" t="n">
@@ -7347,9 +7473,10 @@
       <c r="M124" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N124" s="11"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="40" t="s">
+      <c r="A125" s="41" t="s">
         <v>311</v>
       </c>
       <c r="B125" s="8" t="s">
@@ -7361,10 +7488,10 @@
       <c r="D125" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="41" t="s">
+      <c r="E125" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="F125" s="41" t="s">
+      <c r="F125" s="42" t="s">
         <v>313</v>
       </c>
       <c r="G125" s="10" t="n">
@@ -7385,9 +7512,10 @@
       <c r="M125" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N125" s="11"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="40" t="s">
+      <c r="A126" s="41" t="s">
         <v>314</v>
       </c>
       <c r="B126" s="8" t="s">
@@ -7399,10 +7527,10 @@
       <c r="D126" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E126" s="41" t="s">
+      <c r="E126" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="F126" s="41" t="s">
+      <c r="F126" s="42" t="s">
         <v>316</v>
       </c>
       <c r="G126" s="10" t="n">
@@ -7429,9 +7557,10 @@
         <f aca="false">1000 * 0.000001 / 12</f>
         <v>8.33333333333333E-005</v>
       </c>
+      <c r="N126" s="11"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="40" t="s">
+      <c r="A127" s="41" t="s">
         <v>317</v>
       </c>
       <c r="B127" s="8" t="s">
@@ -7443,10 +7572,10 @@
       <c r="D127" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E127" s="41" t="s">
+      <c r="E127" s="42" t="s">
         <v>318</v>
       </c>
-      <c r="F127" s="41" t="s">
+      <c r="F127" s="42" t="s">
         <v>35</v>
       </c>
       <c r="G127" s="10" t="s">
@@ -7467,9 +7596,10 @@
       <c r="M127" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N127" s="11"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="42" t="s">
+      <c r="A128" s="43" t="s">
         <v>319</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -7481,10 +7611,10 @@
       <c r="D128" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E128" s="43" t="s">
+      <c r="E128" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="F128" s="43" t="s">
+      <c r="F128" s="44" t="s">
         <v>321</v>
       </c>
       <c r="G128" s="10" t="n">
@@ -7505,9 +7635,10 @@
       <c r="M128" s="10" t="n">
         <v>0.0005</v>
       </c>
+      <c r="N128" s="11"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="42" t="s">
+      <c r="A129" s="43" t="s">
         <v>322</v>
       </c>
       <c r="B129" s="8" t="s">
@@ -7519,10 +7650,10 @@
       <c r="D129" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E129" s="43" t="s">
+      <c r="E129" s="44" t="s">
         <v>323</v>
       </c>
-      <c r="F129" s="43" t="s">
+      <c r="F129" s="44" t="s">
         <v>324</v>
       </c>
       <c r="G129" s="10" t="n">
@@ -7548,9 +7679,10 @@
         <f aca="false">0.0000000000005/100/2 * 2</f>
         <v>5E-015</v>
       </c>
+      <c r="N129" s="11"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="42" t="s">
+      <c r="A130" s="43" t="s">
         <v>325</v>
       </c>
       <c r="B130" s="8" t="s">
@@ -7562,10 +7694,10 @@
       <c r="D130" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E130" s="43" t="s">
+      <c r="E130" s="44" t="s">
         <v>323</v>
       </c>
-      <c r="F130" s="43" t="s">
+      <c r="F130" s="44" t="s">
         <v>324</v>
       </c>
       <c r="G130" s="10" t="n">
@@ -7591,9 +7723,10 @@
         <f aca="false">0.000005/3600/100</f>
         <v>1.38888888888889E-011</v>
       </c>
+      <c r="N130" s="11"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="42" t="s">
+      <c r="A131" s="43" t="s">
         <v>326</v>
       </c>
       <c r="B131" s="8" t="s">
@@ -7605,10 +7738,10 @@
       <c r="D131" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E131" s="43" t="s">
+      <c r="E131" s="44" t="s">
         <v>327</v>
       </c>
-      <c r="F131" s="43" t="s">
+      <c r="F131" s="44" t="s">
         <v>244</v>
       </c>
       <c r="G131" s="10" t="n">
@@ -7629,9 +7762,10 @@
       <c r="M131" s="10" t="n">
         <v>10</v>
       </c>
+      <c r="N131" s="11"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="42" t="s">
+      <c r="A132" s="43" t="s">
         <v>328</v>
       </c>
       <c r="B132" s="8" t="s">
@@ -7643,10 +7777,10 @@
       <c r="D132" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E132" s="43" t="s">
+      <c r="E132" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="F132" s="43" t="s">
+      <c r="F132" s="44" t="s">
         <v>330</v>
       </c>
       <c r="G132" s="10" t="n">
@@ -7667,9 +7801,10 @@
       <c r="M132" s="10" t="n">
         <v>-0.04</v>
       </c>
+      <c r="N132" s="11"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="42" t="s">
+      <c r="A133" s="43" t="s">
         <v>331</v>
       </c>
       <c r="B133" s="8" t="s">
@@ -7681,10 +7816,10 @@
       <c r="D133" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="43" t="s">
+      <c r="E133" s="44" t="s">
         <v>332</v>
       </c>
-      <c r="F133" s="43" t="s">
+      <c r="F133" s="44" t="s">
         <v>193</v>
       </c>
       <c r="G133" s="10" t="n">
@@ -7705,9 +7840,10 @@
       <c r="M133" s="10" t="n">
         <v>2.9</v>
       </c>
+      <c r="N133" s="11"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="42" t="s">
+      <c r="A134" s="43" t="s">
         <v>333</v>
       </c>
       <c r="B134" s="8" t="s">
@@ -7719,10 +7855,10 @@
       <c r="D134" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E134" s="43" t="s">
+      <c r="E134" s="44" t="s">
         <v>334</v>
       </c>
-      <c r="F134" s="43" t="s">
+      <c r="F134" s="44" t="s">
         <v>39</v>
       </c>
       <c r="G134" s="10" t="n">
@@ -7743,9 +7879,10 @@
       <c r="M134" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N134" s="11"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="42" t="s">
+      <c r="A135" s="43" t="s">
         <v>335</v>
       </c>
       <c r="B135" s="8" t="s">
@@ -7757,10 +7894,10 @@
       <c r="D135" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E135" s="43" t="s">
+      <c r="E135" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="F135" s="43" t="s">
+      <c r="F135" s="44" t="s">
         <v>313</v>
       </c>
       <c r="G135" s="10" t="n">
@@ -7781,9 +7918,10 @@
       <c r="M135" s="10" t="n">
         <v>2E-007</v>
       </c>
+      <c r="N135" s="11"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="42" t="s">
+      <c r="A136" s="43" t="s">
         <v>336</v>
       </c>
       <c r="B136" s="8" t="s">
@@ -7795,38 +7933,39 @@
       <c r="D136" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E136" s="43" t="s">
+      <c r="E136" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="F136" s="43" t="s">
+      <c r="F136" s="44" t="s">
         <v>244</v>
       </c>
       <c r="G136" s="10" t="n">
         <v>2E-007</v>
       </c>
-      <c r="I136" s="44" t="n">
+      <c r="I136" s="45" t="n">
         <f aca="false">0.0000002*100</f>
         <v>2E-005</v>
       </c>
-      <c r="J136" s="44" t="n">
+      <c r="J136" s="45" t="n">
         <f aca="false">0.0000002*100</f>
         <v>2E-005</v>
       </c>
-      <c r="K136" s="44" t="n">
+      <c r="K136" s="45" t="n">
         <f aca="false">0.0000002*100</f>
         <v>2E-005</v>
       </c>
-      <c r="L136" s="44" t="n">
+      <c r="L136" s="45" t="n">
         <f aca="false">0.0000002*100</f>
         <v>2E-005</v>
       </c>
-      <c r="M136" s="44" t="n">
+      <c r="M136" s="45" t="n">
         <f aca="false">0.0000002*100</f>
         <v>2E-005</v>
       </c>
+      <c r="N136" s="11"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="42" t="s">
+      <c r="A137" s="43" t="s">
         <v>338</v>
       </c>
       <c r="B137" s="8" t="s">
@@ -7838,10 +7977,10 @@
       <c r="D137" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E137" s="43" t="s">
+      <c r="E137" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="F137" s="43" t="s">
+      <c r="F137" s="44" t="s">
         <v>244</v>
       </c>
       <c r="G137" s="10" t="n">
@@ -7862,9 +8001,10 @@
       <c r="M137" s="10" t="n">
         <v>10</v>
       </c>
+      <c r="N137" s="11"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="42" t="s">
+      <c r="A138" s="43" t="s">
         <v>339</v>
       </c>
       <c r="B138" s="8" t="s">
@@ -7876,10 +8016,10 @@
       <c r="D138" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E138" s="43" t="s">
+      <c r="E138" s="44" t="s">
         <v>340</v>
       </c>
-      <c r="F138" s="43" t="s">
+      <c r="F138" s="44" t="s">
         <v>330</v>
       </c>
       <c r="G138" s="10" t="n">
@@ -7900,9 +8040,10 @@
       <c r="M138" s="10" t="n">
         <v>-0.04</v>
       </c>
+      <c r="N138" s="11"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="42" t="s">
+      <c r="A139" s="43" t="s">
         <v>341</v>
       </c>
       <c r="B139" s="8" t="s">
@@ -7914,10 +8055,10 @@
       <c r="D139" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E139" s="43" t="s">
+      <c r="E139" s="44" t="s">
         <v>342</v>
       </c>
-      <c r="F139" s="43" t="s">
+      <c r="F139" s="44" t="s">
         <v>193</v>
       </c>
       <c r="G139" s="10" t="n">
@@ -7938,9 +8079,10 @@
       <c r="M139" s="10" t="n">
         <v>2.9</v>
       </c>
+      <c r="N139" s="11"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="42" t="s">
+      <c r="A140" s="43" t="s">
         <v>343</v>
       </c>
       <c r="B140" s="8" t="s">
@@ -7952,10 +8094,10 @@
       <c r="D140" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E140" s="43" t="s">
+      <c r="E140" s="44" t="s">
         <v>344</v>
       </c>
-      <c r="F140" s="43" t="s">
+      <c r="F140" s="44" t="s">
         <v>39</v>
       </c>
       <c r="G140" s="10" t="n">
@@ -7976,9 +8118,10 @@
       <c r="M140" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N140" s="11"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="42" t="s">
+      <c r="A141" s="43" t="s">
         <v>345</v>
       </c>
       <c r="B141" s="8" t="s">
@@ -7990,10 +8133,10 @@
       <c r="D141" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E141" s="43" t="s">
+      <c r="E141" s="44" t="s">
         <v>346</v>
       </c>
-      <c r="F141" s="43" t="s">
+      <c r="F141" s="44" t="s">
         <v>193</v>
       </c>
       <c r="G141" s="10" t="n">
@@ -8014,9 +8157,10 @@
       <c r="M141" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N141" s="11"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="45" t="s">
+      <c r="A142" s="46" t="s">
         <v>347</v>
       </c>
       <c r="B142" s="8" t="s">
@@ -8028,10 +8172,10 @@
       <c r="D142" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E142" s="46" t="s">
+      <c r="E142" s="47" t="s">
         <v>348</v>
       </c>
-      <c r="F142" s="46" t="s">
+      <c r="F142" s="47" t="s">
         <v>301</v>
       </c>
       <c r="G142" s="10" t="n">
@@ -8057,9 +8201,10 @@
         <f aca="false">0.01*3</f>
         <v>0.03</v>
       </c>
+      <c r="N142" s="11"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="38" t="s">
+      <c r="A143" s="39" t="s">
         <v>349</v>
       </c>
       <c r="B143" s="8" t="s">
@@ -8071,10 +8216,10 @@
       <c r="D143" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E143" s="39" t="s">
+      <c r="E143" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="F143" s="39" t="s">
+      <c r="F143" s="40" t="s">
         <v>301</v>
       </c>
       <c r="G143" s="10" t="n">
@@ -8095,9 +8240,10 @@
       <c r="M143" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N143" s="11"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="38" t="s">
+      <c r="A144" s="39" t="s">
         <v>351</v>
       </c>
       <c r="B144" s="8" t="s">
@@ -8109,10 +8255,10 @@
       <c r="D144" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E144" s="39" t="s">
+      <c r="E144" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="F144" s="39" t="s">
+      <c r="F144" s="40" t="s">
         <v>301</v>
       </c>
       <c r="G144" s="10" t="n">
@@ -8133,9 +8279,10 @@
       <c r="M144" s="10" t="n">
         <v>0.002</v>
       </c>
+      <c r="N144" s="11"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="38" t="s">
+      <c r="A145" s="39" t="s">
         <v>353</v>
       </c>
       <c r="B145" s="8" t="s">
@@ -8147,10 +8294,10 @@
       <c r="D145" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E145" s="39" t="s">
+      <c r="E145" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="F145" s="39" t="s">
+      <c r="F145" s="40" t="s">
         <v>301</v>
       </c>
       <c r="G145" s="10" t="n">
@@ -8171,9 +8318,10 @@
       <c r="M145" s="10" t="n">
         <v>4E-006</v>
       </c>
+      <c r="N145" s="11"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="38" t="s">
+      <c r="A146" s="39" t="s">
         <v>355</v>
       </c>
       <c r="B146" s="8" t="s">
@@ -8185,10 +8333,10 @@
       <c r="D146" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E146" s="39" t="s">
+      <c r="E146" s="40" t="s">
         <v>356</v>
       </c>
-      <c r="F146" s="39" t="s">
+      <c r="F146" s="40" t="s">
         <v>357</v>
       </c>
       <c r="G146" s="10" t="n">
@@ -8209,9 +8357,10 @@
       <c r="M146" s="10" t="n">
         <v>3.77E-010</v>
       </c>
+      <c r="N146" s="11"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="38" t="s">
+      <c r="A147" s="39" t="s">
         <v>358</v>
       </c>
       <c r="B147" s="8" t="s">
@@ -8223,10 +8372,10 @@
       <c r="D147" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E147" s="39" t="s">
+      <c r="E147" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="F147" s="39" t="s">
+      <c r="F147" s="40" t="s">
         <v>244</v>
       </c>
       <c r="G147" s="10" t="n">
@@ -8247,9 +8396,10 @@
       <c r="M147" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N147" s="11"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="38" t="s">
+      <c r="A148" s="39" t="s">
         <v>360</v>
       </c>
       <c r="B148" s="8" t="s">
@@ -8261,10 +8411,10 @@
       <c r="D148" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E148" s="39" t="s">
+      <c r="E148" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="F148" s="39" t="s">
+      <c r="F148" s="40" t="s">
         <v>330</v>
       </c>
       <c r="G148" s="10" t="n">
@@ -8285,9 +8435,10 @@
       <c r="M148" s="10" t="n">
         <v>-0.06</v>
       </c>
+      <c r="N148" s="11"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="38" t="s">
+      <c r="A149" s="39" t="s">
         <v>362</v>
       </c>
       <c r="B149" s="8" t="s">
@@ -8299,10 +8450,10 @@
       <c r="D149" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E149" s="39" t="s">
+      <c r="E149" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="F149" s="39" t="s">
+      <c r="F149" s="40" t="s">
         <v>193</v>
       </c>
       <c r="G149" s="10" t="n">
@@ -8323,9 +8474,10 @@
       <c r="M149" s="10" t="n">
         <v>0.891</v>
       </c>
+      <c r="N149" s="11"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="38" t="s">
+      <c r="A150" s="39" t="s">
         <v>364</v>
       </c>
       <c r="B150" s="8" t="s">
@@ -8337,10 +8489,10 @@
       <c r="D150" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E150" s="39" t="s">
+      <c r="E150" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="F150" s="39" t="s">
+      <c r="F150" s="40" t="s">
         <v>39</v>
       </c>
       <c r="G150" s="10" t="n">
@@ -8361,9 +8513,10 @@
       <c r="M150" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N150" s="11"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="38" t="s">
+      <c r="A151" s="39" t="s">
         <v>366</v>
       </c>
       <c r="B151" s="8" t="s">
@@ -8375,10 +8528,10 @@
       <c r="D151" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E151" s="39" t="s">
+      <c r="E151" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="F151" s="39" t="s">
+      <c r="F151" s="40" t="s">
         <v>301</v>
       </c>
       <c r="G151" s="10" t="n">
@@ -8399,9 +8552,10 @@
       <c r="M151" s="10" t="n">
         <v>4E-005</v>
       </c>
+      <c r="N151" s="11"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="25" t="s">
+      <c r="A152" s="26" t="s">
         <v>368</v>
       </c>
       <c r="B152" s="8" t="s">
@@ -8413,10 +8567,10 @@
       <c r="D152" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E152" s="26" t="s">
+      <c r="E152" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="F152" s="26" t="s">
+      <c r="F152" s="27" t="s">
         <v>357</v>
       </c>
       <c r="G152" s="10" t="n">
@@ -8437,9 +8591,10 @@
       <c r="M152" s="10" t="n">
         <v>5.83333333333333E-009</v>
       </c>
+      <c r="N152" s="11"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="25" t="s">
+      <c r="A153" s="26" t="s">
         <v>370</v>
       </c>
       <c r="B153" s="8" t="s">
@@ -8451,10 +8606,10 @@
       <c r="D153" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E153" s="26" t="s">
+      <c r="E153" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="F153" s="26" t="s">
+      <c r="F153" s="27" t="s">
         <v>244</v>
       </c>
       <c r="G153" s="10" t="n">
@@ -8475,9 +8630,10 @@
       <c r="M153" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N153" s="11"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="25" t="s">
+      <c r="A154" s="26" t="s">
         <v>372</v>
       </c>
       <c r="B154" s="8" t="s">
@@ -8489,10 +8645,10 @@
       <c r="D154" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E154" s="26" t="s">
+      <c r="E154" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="F154" s="26" t="s">
+      <c r="F154" s="27" t="s">
         <v>330</v>
       </c>
       <c r="G154" s="10" t="n">
@@ -8513,9 +8669,10 @@
       <c r="M154" s="10" t="n">
         <v>-0.06</v>
       </c>
+      <c r="N154" s="11"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="25" t="s">
+      <c r="A155" s="26" t="s">
         <v>374</v>
       </c>
       <c r="B155" s="8" t="s">
@@ -8527,10 +8684,10 @@
       <c r="D155" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E155" s="26" t="s">
+      <c r="E155" s="27" t="s">
         <v>375</v>
       </c>
-      <c r="F155" s="26" t="s">
+      <c r="F155" s="27" t="s">
         <v>193</v>
       </c>
       <c r="G155" s="10" t="n">
@@ -8551,9 +8708,10 @@
       <c r="M155" s="10" t="n">
         <v>0.891</v>
       </c>
+      <c r="N155" s="11"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="25" t="s">
+      <c r="A156" s="26" t="s">
         <v>376</v>
       </c>
       <c r="B156" s="8" t="s">
@@ -8565,10 +8723,10 @@
       <c r="D156" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E156" s="26" t="s">
+      <c r="E156" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="F156" s="26" t="s">
+      <c r="F156" s="27" t="s">
         <v>39</v>
       </c>
       <c r="G156" s="10" t="n">
@@ -8589,9 +8747,10 @@
       <c r="M156" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N156" s="11"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="25" t="s">
+      <c r="A157" s="26" t="s">
         <v>378</v>
       </c>
       <c r="B157" s="8" t="s">
@@ -8603,10 +8762,10 @@
       <c r="D157" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E157" s="26" t="s">
+      <c r="E157" s="27" t="s">
         <v>379</v>
       </c>
-      <c r="F157" s="26" t="s">
+      <c r="F157" s="27" t="s">
         <v>301</v>
       </c>
       <c r="G157" s="10" t="n">
@@ -8627,9 +8786,10 @@
       <c r="M157" s="10" t="n">
         <v>4E-005</v>
       </c>
+      <c r="N157" s="11"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="22" t="s">
+      <c r="A158" s="23" t="s">
         <v>380</v>
       </c>
       <c r="B158" s="8" t="s">
@@ -8641,10 +8801,10 @@
       <c r="D158" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E158" s="23" t="s">
+      <c r="E158" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="F158" s="23" t="s">
+      <c r="F158" s="24" t="s">
         <v>357</v>
       </c>
       <c r="G158" s="10" t="n">
@@ -8665,9 +8825,10 @@
       <c r="M158" s="10" t="n">
         <v>4E-008</v>
       </c>
+      <c r="N158" s="11"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="22" t="s">
+      <c r="A159" s="23" t="s">
         <v>382</v>
       </c>
       <c r="B159" s="8" t="s">
@@ -8679,10 +8840,10 @@
       <c r="D159" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E159" s="23" t="s">
+      <c r="E159" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="F159" s="23" t="s">
+      <c r="F159" s="24" t="s">
         <v>244</v>
       </c>
       <c r="G159" s="10" t="n">
@@ -8703,9 +8864,10 @@
       <c r="M159" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N159" s="11"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="22" t="s">
+      <c r="A160" s="23" t="s">
         <v>384</v>
       </c>
       <c r="B160" s="8" t="s">
@@ -8717,10 +8879,10 @@
       <c r="D160" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E160" s="23" t="s">
+      <c r="E160" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="F160" s="23" t="s">
+      <c r="F160" s="24" t="s">
         <v>330</v>
       </c>
       <c r="G160" s="10" t="n">
@@ -8741,9 +8903,10 @@
       <c r="M160" s="10" t="n">
         <v>-0.0442</v>
       </c>
+      <c r="N160" s="11"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="22" t="s">
+      <c r="A161" s="23" t="s">
         <v>386</v>
       </c>
       <c r="B161" s="8" t="s">
@@ -8755,10 +8918,10 @@
       <c r="D161" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E161" s="23" t="s">
+      <c r="E161" s="24" t="s">
         <v>387</v>
       </c>
-      <c r="F161" s="23" t="s">
+      <c r="F161" s="24" t="s">
         <v>193</v>
       </c>
       <c r="G161" s="10" t="n">
@@ -8779,9 +8942,10 @@
       <c r="M161" s="10" t="n">
         <v>1.55</v>
       </c>
+      <c r="N161" s="11"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="22" t="s">
+      <c r="A162" s="23" t="s">
         <v>388</v>
       </c>
       <c r="B162" s="8" t="s">
@@ -8793,10 +8957,10 @@
       <c r="D162" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E162" s="23" t="s">
+      <c r="E162" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="F162" s="23" t="s">
+      <c r="F162" s="24" t="s">
         <v>39</v>
       </c>
       <c r="G162" s="10" t="n">
@@ -8817,9 +8981,10 @@
       <c r="M162" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N162" s="11"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="22" t="s">
+      <c r="A163" s="23" t="s">
         <v>390</v>
       </c>
       <c r="B163" s="8" t="s">
@@ -8831,10 +8996,10 @@
       <c r="D163" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E163" s="23" t="s">
+      <c r="E163" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="F163" s="23" t="s">
+      <c r="F163" s="24" t="s">
         <v>301</v>
       </c>
       <c r="G163" s="10" t="n">
@@ -8855,9 +9020,10 @@
       <c r="M163" s="10" t="n">
         <v>0.000278</v>
       </c>
+      <c r="N163" s="11"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="47" t="s">
+      <c r="A164" s="48" t="s">
         <v>392</v>
       </c>
       <c r="B164" s="8" t="s">
@@ -8869,10 +9035,10 @@
       <c r="D164" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E164" s="48" t="s">
+      <c r="E164" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="F164" s="48" t="s">
+      <c r="F164" s="49" t="s">
         <v>394</v>
       </c>
       <c r="G164" s="10" t="n">
@@ -8898,9 +9064,10 @@
         <f aca="false">0.0000000000025/5</f>
         <v>5E-013</v>
       </c>
+      <c r="N164" s="11"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="47" t="s">
+      <c r="A165" s="48" t="s">
         <v>395</v>
       </c>
       <c r="B165" s="8" t="s">
@@ -8912,10 +9079,10 @@
       <c r="D165" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="48" t="s">
+      <c r="E165" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="F165" s="48" t="s">
+      <c r="F165" s="49" t="s">
         <v>244</v>
       </c>
       <c r="G165" s="10" t="n">
@@ -8936,9 +9103,10 @@
       <c r="M165" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N165" s="11"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="47" t="s">
+      <c r="A166" s="48" t="s">
         <v>397</v>
       </c>
       <c r="B166" s="8" t="s">
@@ -8950,10 +9118,10 @@
       <c r="D166" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E166" s="48" t="s">
+      <c r="E166" s="49" t="s">
         <v>398</v>
       </c>
-      <c r="F166" s="48" t="s">
+      <c r="F166" s="49" t="s">
         <v>330</v>
       </c>
       <c r="G166" s="10" t="n">
@@ -8974,9 +9142,10 @@
       <c r="M166" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N166" s="11"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="47" t="s">
+      <c r="A167" s="48" t="s">
         <v>399</v>
       </c>
       <c r="B167" s="8" t="s">
@@ -8988,10 +9157,10 @@
       <c r="D167" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E167" s="48" t="s">
+      <c r="E167" s="49" t="s">
         <v>400</v>
       </c>
-      <c r="F167" s="48" t="s">
+      <c r="F167" s="49" t="s">
         <v>193</v>
       </c>
       <c r="G167" s="10" t="n">
@@ -9012,9 +9181,10 @@
       <c r="M167" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N167" s="11"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="47" t="s">
+      <c r="A168" s="48" t="s">
         <v>401</v>
       </c>
       <c r="B168" s="8" t="s">
@@ -9026,10 +9196,10 @@
       <c r="D168" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E168" s="48" t="s">
+      <c r="E168" s="49" t="s">
         <v>402</v>
       </c>
-      <c r="F168" s="48" t="s">
+      <c r="F168" s="49" t="s">
         <v>39</v>
       </c>
       <c r="G168" s="10" t="n">
@@ -9050,9 +9220,10 @@
       <c r="M168" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N168" s="11"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="47" t="s">
+      <c r="A169" s="48" t="s">
         <v>403</v>
       </c>
       <c r="B169" s="8" t="s">
@@ -9064,10 +9235,10 @@
       <c r="D169" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E169" s="48" t="s">
+      <c r="E169" s="49" t="s">
         <v>404</v>
       </c>
-      <c r="F169" s="48" t="s">
+      <c r="F169" s="49" t="s">
         <v>193</v>
       </c>
       <c r="G169" s="10" t="n">
@@ -9088,9 +9259,10 @@
       <c r="M169" s="10" t="n">
         <v>0.4</v>
       </c>
+      <c r="N169" s="11"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="49" t="s">
+      <c r="A170" s="50" t="s">
         <v>405</v>
       </c>
       <c r="B170" s="8" t="s">
@@ -9102,10 +9274,10 @@
       <c r="D170" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E170" s="50" t="s">
+      <c r="E170" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="F170" s="50" t="s">
+      <c r="F170" s="51" t="s">
         <v>357</v>
       </c>
       <c r="G170" s="10" t="n">
@@ -9126,9 +9298,10 @@
       <c r="M170" s="10" t="n">
         <v>2E-009</v>
       </c>
+      <c r="N170" s="11"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="49" t="s">
+      <c r="A171" s="50" t="s">
         <v>407</v>
       </c>
       <c r="B171" s="8" t="s">
@@ -9140,10 +9313,10 @@
       <c r="D171" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E171" s="50" t="s">
+      <c r="E171" s="51" t="s">
         <v>408</v>
       </c>
-      <c r="F171" s="50" t="s">
+      <c r="F171" s="51" t="s">
         <v>244</v>
       </c>
       <c r="G171" s="10" t="n">
@@ -9164,9 +9337,10 @@
       <c r="M171" s="10" t="n">
         <v>25</v>
       </c>
+      <c r="N171" s="11"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="49" t="s">
+      <c r="A172" s="50" t="s">
         <v>409</v>
       </c>
       <c r="B172" s="8" t="s">
@@ -9178,10 +9352,10 @@
       <c r="D172" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E172" s="50" t="s">
+      <c r="E172" s="51" t="s">
         <v>410</v>
       </c>
-      <c r="F172" s="50" t="s">
+      <c r="F172" s="51" t="s">
         <v>330</v>
       </c>
       <c r="G172" s="10" t="n">
@@ -9202,9 +9376,10 @@
       <c r="M172" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N172" s="11"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="49" t="s">
+      <c r="A173" s="50" t="s">
         <v>411</v>
       </c>
       <c r="B173" s="8" t="s">
@@ -9216,10 +9391,10 @@
       <c r="D173" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E173" s="50" t="s">
+      <c r="E173" s="51" t="s">
         <v>412</v>
       </c>
-      <c r="F173" s="50" t="s">
+      <c r="F173" s="51" t="s">
         <v>193</v>
       </c>
       <c r="G173" s="10" t="n">
@@ -9240,9 +9415,10 @@
       <c r="M173" s="10" t="n">
         <v>3.98</v>
       </c>
+      <c r="N173" s="11"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="49" t="s">
+      <c r="A174" s="50" t="s">
         <v>413</v>
       </c>
       <c r="B174" s="8" t="s">
@@ -9254,10 +9430,10 @@
       <c r="D174" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E174" s="50" t="s">
+      <c r="E174" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="F174" s="50" t="s">
+      <c r="F174" s="51" t="s">
         <v>39</v>
       </c>
       <c r="G174" s="10" t="n">
@@ -9278,9 +9454,10 @@
       <c r="M174" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N174" s="11"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="49" t="s">
+      <c r="A175" s="50" t="s">
         <v>415</v>
       </c>
       <c r="B175" s="8" t="s">
@@ -9292,10 +9469,10 @@
       <c r="D175" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E175" s="50" t="s">
+      <c r="E175" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="F175" s="50" t="s">
+      <c r="F175" s="51" t="s">
         <v>301</v>
       </c>
       <c r="G175" s="10" t="n">
@@ -9316,9 +9493,10 @@
       <c r="M175" s="10" t="n">
         <v>0.000166666666666667</v>
       </c>
+      <c r="N175" s="11"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="28" t="s">
+      <c r="A176" s="29" t="s">
         <v>417</v>
       </c>
       <c r="B176" s="8" t="s">
@@ -9330,10 +9508,10 @@
       <c r="D176" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E176" s="29" t="s">
+      <c r="E176" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="F176" s="29" t="s">
+      <c r="F176" s="30" t="s">
         <v>419</v>
       </c>
       <c r="G176" s="10" t="n">
@@ -9354,9 +9532,10 @@
       <c r="M176" s="10" t="n">
         <v>1E-008</v>
       </c>
+      <c r="N176" s="11"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="28" t="s">
+      <c r="A177" s="29" t="s">
         <v>420</v>
       </c>
       <c r="B177" s="8" t="s">
@@ -9368,10 +9547,10 @@
       <c r="D177" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E177" s="29" t="s">
+      <c r="E177" s="30" t="s">
         <v>421</v>
       </c>
-      <c r="F177" s="29" t="s">
+      <c r="F177" s="30" t="s">
         <v>244</v>
       </c>
       <c r="G177" s="10" t="n">
@@ -9392,9 +9571,10 @@
       <c r="M177" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N177" s="11"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="28" t="s">
+      <c r="A178" s="29" t="s">
         <v>422</v>
       </c>
       <c r="B178" s="8" t="s">
@@ -9406,10 +9586,10 @@
       <c r="D178" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E178" s="29" t="s">
+      <c r="E178" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="F178" s="29" t="s">
+      <c r="F178" s="30" t="s">
         <v>330</v>
       </c>
       <c r="G178" s="10" t="n">
@@ -9430,9 +9610,10 @@
       <c r="M178" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N178" s="11"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="28" t="s">
+      <c r="A179" s="29" t="s">
         <v>424</v>
       </c>
       <c r="B179" s="8" t="s">
@@ -9444,10 +9625,10 @@
       <c r="D179" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E179" s="29" t="s">
+      <c r="E179" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="F179" s="29" t="s">
+      <c r="F179" s="30" t="s">
         <v>193</v>
       </c>
       <c r="G179" s="10" t="n">
@@ -9468,9 +9649,10 @@
       <c r="M179" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="N179" s="11"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="28" t="s">
+      <c r="A180" s="29" t="s">
         <v>426</v>
       </c>
       <c r="B180" s="8" t="s">
@@ -9482,10 +9664,10 @@
       <c r="D180" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E180" s="29" t="s">
+      <c r="E180" s="30" t="s">
         <v>427</v>
       </c>
-      <c r="F180" s="29" t="s">
+      <c r="F180" s="30" t="s">
         <v>39</v>
       </c>
       <c r="G180" s="10" t="n">
@@ -9506,9 +9688,10 @@
       <c r="M180" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N180" s="11"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="28" t="s">
+      <c r="A181" s="29" t="s">
         <v>428</v>
       </c>
       <c r="B181" s="8" t="s">
@@ -9520,10 +9703,10 @@
       <c r="D181" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E181" s="29" t="s">
+      <c r="E181" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="F181" s="29" t="s">
+      <c r="F181" s="30" t="s">
         <v>301</v>
       </c>
       <c r="G181" s="10" t="n">
@@ -9544,9 +9727,10 @@
       <c r="M181" s="10" t="n">
         <v>8.33333333333333E-005</v>
       </c>
+      <c r="N181" s="11"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="28" t="s">
+      <c r="A182" s="29" t="s">
         <v>430</v>
       </c>
       <c r="B182" s="8" t="s">
@@ -9558,10 +9742,10 @@
       <c r="D182" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E182" s="29" t="s">
+      <c r="E182" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="F182" s="29" t="s">
+      <c r="F182" s="30" t="s">
         <v>193</v>
       </c>
       <c r="G182" s="10" t="n">
@@ -9582,9 +9766,10 @@
       <c r="M182" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N182" s="11"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="51" t="s">
+      <c r="A183" s="52" t="s">
         <v>432</v>
       </c>
       <c r="B183" s="8" t="s">
@@ -9596,10 +9781,10 @@
       <c r="D183" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E183" s="52" t="s">
+      <c r="E183" s="53" t="s">
         <v>433</v>
       </c>
-      <c r="F183" s="52" t="s">
+      <c r="F183" s="53" t="s">
         <v>434</v>
       </c>
       <c r="G183" s="10" t="n">
@@ -9620,9 +9805,10 @@
       <c r="M183" s="10" t="n">
         <v>2.35330507911489E-008</v>
       </c>
+      <c r="N183" s="11"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="51" t="s">
+      <c r="A184" s="52" t="s">
         <v>435</v>
       </c>
       <c r="B184" s="8" t="s">
@@ -9634,10 +9820,10 @@
       <c r="D184" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E184" s="52" t="s">
+      <c r="E184" s="53" t="s">
         <v>436</v>
       </c>
-      <c r="F184" s="52" t="s">
+      <c r="F184" s="53" t="s">
         <v>244</v>
       </c>
       <c r="G184" s="10" t="n">
@@ -9658,9 +9844,10 @@
       <c r="M184" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="N184" s="11"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="51" t="s">
+      <c r="A185" s="52" t="s">
         <v>437</v>
       </c>
       <c r="B185" s="8" t="s">
@@ -9672,10 +9859,10 @@
       <c r="D185" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E185" s="52" t="s">
+      <c r="E185" s="53" t="s">
         <v>438</v>
       </c>
-      <c r="F185" s="52" t="s">
+      <c r="F185" s="53" t="s">
         <v>330</v>
       </c>
       <c r="G185" s="10" t="n">
@@ -9696,9 +9883,10 @@
       <c r="M185" s="10" t="n">
         <v>-0.187</v>
       </c>
+      <c r="N185" s="11"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="51" t="s">
+      <c r="A186" s="52" t="s">
         <v>439</v>
       </c>
       <c r="B186" s="8" t="s">
@@ -9710,10 +9898,10 @@
       <c r="D186" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E186" s="52" t="s">
+      <c r="E186" s="53" t="s">
         <v>440</v>
       </c>
-      <c r="F186" s="52" t="s">
+      <c r="F186" s="53" t="s">
         <v>193</v>
       </c>
       <c r="G186" s="10" t="n">
@@ -9734,9 +9922,10 @@
       <c r="M186" s="10" t="n">
         <v>2.48</v>
       </c>
+      <c r="N186" s="11"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="51" t="s">
+      <c r="A187" s="52" t="s">
         <v>441</v>
       </c>
       <c r="B187" s="8" t="s">
@@ -9748,10 +9937,10 @@
       <c r="D187" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E187" s="52" t="s">
+      <c r="E187" s="53" t="s">
         <v>442</v>
       </c>
-      <c r="F187" s="52" t="s">
+      <c r="F187" s="53" t="s">
         <v>39</v>
       </c>
       <c r="G187" s="10" t="n">
@@ -9772,9 +9961,10 @@
       <c r="M187" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N187" s="11"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="51" t="s">
+      <c r="A188" s="52" t="s">
         <v>443</v>
       </c>
       <c r="B188" s="8" t="s">
@@ -9786,10 +9976,10 @@
       <c r="D188" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E188" s="52" t="s">
+      <c r="E188" s="53" t="s">
         <v>444</v>
       </c>
-      <c r="F188" s="52" t="s">
+      <c r="F188" s="53" t="s">
         <v>445</v>
       </c>
       <c r="G188" s="10" t="n">
@@ -9810,9 +10000,10 @@
       <c r="M188" s="10" t="n">
         <v>0.00061060227588121</v>
       </c>
+      <c r="N188" s="11"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="38" t="s">
+      <c r="A189" s="39" t="s">
         <v>446</v>
       </c>
       <c r="B189" s="8" t="s">
@@ -9824,10 +10015,10 @@
       <c r="D189" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E189" s="39" t="s">
+      <c r="E189" s="40" t="s">
         <v>447</v>
       </c>
-      <c r="F189" s="39" t="s">
+      <c r="F189" s="40" t="s">
         <v>357</v>
       </c>
       <c r="G189" s="10" t="n">
@@ -9848,9 +10039,10 @@
       <c r="M189" s="10" t="n">
         <v>4E-007</v>
       </c>
+      <c r="N189" s="11"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="38" t="s">
+      <c r="A190" s="39" t="s">
         <v>448</v>
       </c>
       <c r="B190" s="8" t="s">
@@ -9862,10 +10054,10 @@
       <c r="D190" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E190" s="39" t="s">
+      <c r="E190" s="40" t="s">
         <v>449</v>
       </c>
-      <c r="F190" s="39" t="s">
+      <c r="F190" s="40" t="s">
         <v>244</v>
       </c>
       <c r="G190" s="10" t="n">
@@ -9886,9 +10078,10 @@
       <c r="M190" s="10" t="n">
         <v>25</v>
       </c>
+      <c r="N190" s="11"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="38" t="s">
+      <c r="A191" s="39" t="s">
         <v>450</v>
       </c>
       <c r="B191" s="8" t="s">
@@ -9900,10 +10093,10 @@
       <c r="D191" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E191" s="39" t="s">
+      <c r="E191" s="40" t="s">
         <v>451</v>
       </c>
-      <c r="F191" s="39" t="s">
+      <c r="F191" s="40" t="s">
         <v>330</v>
       </c>
       <c r="G191" s="10" t="n">
@@ -9924,9 +10117,10 @@
       <c r="M191" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N191" s="11"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="38" t="s">
+      <c r="A192" s="39" t="s">
         <v>452</v>
       </c>
       <c r="B192" s="8" t="s">
@@ -9938,10 +10132,10 @@
       <c r="D192" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E192" s="39" t="s">
+      <c r="E192" s="40" t="s">
         <v>453</v>
       </c>
-      <c r="F192" s="39" t="s">
+      <c r="F192" s="40" t="s">
         <v>193</v>
       </c>
       <c r="G192" s="10" t="n">
@@ -9962,9 +10156,10 @@
       <c r="M192" s="10" t="n">
         <v>3.98</v>
       </c>
+      <c r="N192" s="11"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="38" t="s">
+      <c r="A193" s="39" t="s">
         <v>454</v>
       </c>
       <c r="B193" s="8" t="s">
@@ -9976,10 +10171,10 @@
       <c r="D193" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E193" s="39" t="s">
+      <c r="E193" s="40" t="s">
         <v>455</v>
       </c>
-      <c r="F193" s="39" t="s">
+      <c r="F193" s="40" t="s">
         <v>39</v>
       </c>
       <c r="G193" s="10" t="n">
@@ -10000,9 +10195,10 @@
       <c r="M193" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N193" s="11"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="38" t="s">
+      <c r="A194" s="39" t="s">
         <v>456</v>
       </c>
       <c r="B194" s="8" t="s">
@@ -10014,10 +10210,10 @@
       <c r="D194" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E194" s="39" t="s">
+      <c r="E194" s="40" t="s">
         <v>457</v>
       </c>
-      <c r="F194" s="39" t="s">
+      <c r="F194" s="40" t="s">
         <v>301</v>
       </c>
       <c r="G194" s="10" t="n">
@@ -10038,9 +10234,10 @@
       <c r="M194" s="10" t="n">
         <v>8.33333333333333E-005</v>
       </c>
+      <c r="N194" s="11"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="20" t="s">
+      <c r="A195" s="21" t="s">
         <v>458</v>
       </c>
       <c r="B195" s="8" t="s">
@@ -10052,10 +10249,10 @@
       <c r="D195" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E195" s="21" t="s">
+      <c r="E195" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="F195" s="21" t="s">
+      <c r="F195" s="22" t="s">
         <v>357</v>
       </c>
       <c r="G195" s="10" t="n">
@@ -10076,9 +10273,10 @@
       <c r="M195" s="10" t="n">
         <v>4E-007</v>
       </c>
+      <c r="N195" s="11"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="20" t="s">
+      <c r="A196" s="21" t="s">
         <v>460</v>
       </c>
       <c r="B196" s="8" t="s">
@@ -10090,10 +10288,10 @@
       <c r="D196" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E196" s="21" t="s">
+      <c r="E196" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="F196" s="21" t="s">
+      <c r="F196" s="22" t="s">
         <v>244</v>
       </c>
       <c r="G196" s="10" t="n">
@@ -10114,9 +10312,10 @@
       <c r="M196" s="10" t="n">
         <v>25</v>
       </c>
+      <c r="N196" s="11"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="20" t="s">
+      <c r="A197" s="21" t="s">
         <v>462</v>
       </c>
       <c r="B197" s="8" t="s">
@@ -10128,10 +10327,10 @@
       <c r="D197" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E197" s="21" t="s">
+      <c r="E197" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="F197" s="21" t="s">
+      <c r="F197" s="22" t="s">
         <v>330</v>
       </c>
       <c r="G197" s="10" t="n">
@@ -10152,9 +10351,10 @@
       <c r="M197" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N197" s="11"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="20" t="s">
+      <c r="A198" s="21" t="s">
         <v>464</v>
       </c>
       <c r="B198" s="8" t="s">
@@ -10166,10 +10366,10 @@
       <c r="D198" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E198" s="21" t="s">
+      <c r="E198" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="F198" s="21" t="s">
+      <c r="F198" s="22" t="s">
         <v>193</v>
       </c>
       <c r="G198" s="10" t="n">
@@ -10190,9 +10390,10 @@
       <c r="M198" s="10" t="n">
         <v>3.98</v>
       </c>
+      <c r="N198" s="11"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="20" t="s">
+      <c r="A199" s="21" t="s">
         <v>466</v>
       </c>
       <c r="B199" s="8" t="s">
@@ -10204,10 +10405,10 @@
       <c r="D199" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E199" s="21" t="s">
+      <c r="E199" s="22" t="s">
         <v>467</v>
       </c>
-      <c r="F199" s="21" t="s">
+      <c r="F199" s="22" t="s">
         <v>39</v>
       </c>
       <c r="G199" s="10" t="n">
@@ -10228,9 +10429,10 @@
       <c r="M199" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N199" s="11"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="20" t="s">
+      <c r="A200" s="21" t="s">
         <v>468</v>
       </c>
       <c r="B200" s="8" t="s">
@@ -10242,10 +10444,10 @@
       <c r="D200" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E200" s="21" t="s">
+      <c r="E200" s="22" t="s">
         <v>469</v>
       </c>
-      <c r="F200" s="21" t="s">
+      <c r="F200" s="22" t="s">
         <v>301</v>
       </c>
       <c r="G200" s="10" t="n">
@@ -10266,9 +10468,10 @@
       <c r="M200" s="10" t="n">
         <v>8.33333333333333E-005</v>
       </c>
+      <c r="N200" s="11"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="53" t="s">
+      <c r="A201" s="54" t="s">
         <v>470</v>
       </c>
       <c r="B201" s="8" t="s">
@@ -10280,10 +10483,10 @@
       <c r="D201" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E201" s="54" t="s">
+      <c r="E201" s="55" t="s">
         <v>471</v>
       </c>
-      <c r="F201" s="54" t="s">
+      <c r="F201" s="55" t="s">
         <v>472</v>
       </c>
       <c r="G201" s="10" t="n">
@@ -10304,9 +10507,10 @@
       <c r="M201" s="10" t="n">
         <v>2E-007</v>
       </c>
+      <c r="N201" s="11"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="53" t="s">
+      <c r="A202" s="54" t="s">
         <v>473</v>
       </c>
       <c r="B202" s="8" t="s">
@@ -10318,10 +10522,10 @@
       <c r="D202" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E202" s="54" t="s">
+      <c r="E202" s="55" t="s">
         <v>474</v>
       </c>
-      <c r="F202" s="54" t="s">
+      <c r="F202" s="55" t="s">
         <v>244</v>
       </c>
       <c r="G202" s="10" t="n">
@@ -10342,9 +10546,10 @@
       <c r="M202" s="10" t="n">
         <v>25</v>
       </c>
+      <c r="N202" s="11"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="53" t="s">
+      <c r="A203" s="54" t="s">
         <v>475</v>
       </c>
       <c r="B203" s="8" t="s">
@@ -10356,10 +10561,10 @@
       <c r="D203" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E203" s="54" t="s">
+      <c r="E203" s="55" t="s">
         <v>476</v>
       </c>
-      <c r="F203" s="54" t="s">
+      <c r="F203" s="55" t="s">
         <v>330</v>
       </c>
       <c r="G203" s="10" t="n">
@@ -10380,9 +10585,10 @@
       <c r="M203" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N203" s="11"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="53" t="s">
+      <c r="A204" s="54" t="s">
         <v>477</v>
       </c>
       <c r="B204" s="8" t="s">
@@ -10394,10 +10600,10 @@
       <c r="D204" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E204" s="54" t="s">
+      <c r="E204" s="55" t="s">
         <v>478</v>
       </c>
-      <c r="F204" s="54" t="s">
+      <c r="F204" s="55" t="s">
         <v>193</v>
       </c>
       <c r="G204" s="10" t="n">
@@ -10418,9 +10624,10 @@
       <c r="M204" s="10" t="n">
         <v>3.98</v>
       </c>
+      <c r="N204" s="11"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="53" t="s">
+      <c r="A205" s="54" t="s">
         <v>479</v>
       </c>
       <c r="B205" s="8" t="s">
@@ -10432,10 +10639,10 @@
       <c r="D205" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E205" s="54" t="s">
+      <c r="E205" s="55" t="s">
         <v>480</v>
       </c>
-      <c r="F205" s="54" t="s">
+      <c r="F205" s="55" t="s">
         <v>39</v>
       </c>
       <c r="G205" s="10" t="n">
@@ -10456,9 +10663,10 @@
       <c r="M205" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="N205" s="11"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="53" t="s">
+      <c r="A206" s="54" t="s">
         <v>481</v>
       </c>
       <c r="B206" s="8" t="s">
@@ -10470,10 +10678,10 @@
       <c r="D206" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E206" s="54" t="s">
+      <c r="E206" s="55" t="s">
         <v>482</v>
       </c>
-      <c r="F206" s="54" t="s">
+      <c r="F206" s="55" t="s">
         <v>483</v>
       </c>
       <c r="G206" s="10" t="n">
@@ -10494,24 +10702,25 @@
       <c r="M206" s="10" t="n">
         <v>8.33333333333333E-005</v>
       </c>
+      <c r="N206" s="11"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="55" t="s">
+      <c r="A207" s="56" t="s">
         <v>484</v>
       </c>
-      <c r="B207" s="56" t="s">
+      <c r="B207" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="C207" s="56" t="s">
+      <c r="C207" s="57" t="s">
         <v>14</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E207" s="57" t="s">
+      <c r="E207" s="58" t="s">
         <v>485</v>
       </c>
-      <c r="F207" s="57" t="s">
+      <c r="F207" s="58" t="s">
         <v>17</v>
       </c>
       <c r="G207" s="10" t="s">
@@ -10532,6 +10741,7 @@
       <c r="M207" s="10" t="s">
         <v>486</v>
       </c>
+      <c r="N207" s="11"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4" t="s">
@@ -10546,10 +10756,10 @@
       <c r="D208" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E208" s="54" t="s">
+      <c r="E208" s="55" t="s">
         <v>490</v>
       </c>
-      <c r="F208" s="54" t="s">
+      <c r="F208" s="55" t="s">
         <v>491</v>
       </c>
       <c r="G208" s="10" t="n">
@@ -10576,6 +10786,7 @@
         <f aca="false">0.0000005*0.4285*10/2.028*4</f>
         <v>4.2258382642998E-006</v>
       </c>
+      <c r="N208" s="11"/>
       <c r="O208" s="1"/>
       <c r="P208" s="1"/>
       <c r="Q208" s="1"/>
@@ -10598,10 +10809,10 @@
       <c r="D209" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E209" s="54" t="s">
+      <c r="E209" s="55" t="s">
         <v>493</v>
       </c>
-      <c r="F209" s="54" t="s">
+      <c r="F209" s="55" t="s">
         <v>494</v>
       </c>
       <c r="G209" s="10" t="n">
@@ -10622,14 +10833,15 @@
       <c r="M209" s="10" t="n">
         <v>0.31</v>
       </c>
-      <c r="O209" s="58"/>
-      <c r="P209" s="58"/>
-      <c r="Q209" s="58"/>
-      <c r="R209" s="58"/>
-      <c r="S209" s="58"/>
-      <c r="T209" s="58"/>
-      <c r="U209" s="58"/>
-      <c r="V209" s="58"/>
+      <c r="N209" s="11"/>
+      <c r="O209" s="59"/>
+      <c r="P209" s="59"/>
+      <c r="Q209" s="59"/>
+      <c r="R209" s="59"/>
+      <c r="S209" s="59"/>
+      <c r="T209" s="59"/>
+      <c r="U209" s="59"/>
+      <c r="V209" s="59"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4" t="s">
@@ -10644,10 +10856,10 @@
       <c r="D210" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E210" s="59" t="s">
+      <c r="E210" s="60" t="s">
         <v>496</v>
       </c>
-      <c r="F210" s="59" t="s">
+      <c r="F210" s="60" t="s">
         <v>497</v>
       </c>
       <c r="G210" s="10" t="n">
@@ -10674,6 +10886,7 @@
         <f aca="false">0.00002 / 14</f>
         <v>1.42857142857143E-006</v>
       </c>
+      <c r="N210" s="11"/>
       <c r="O210" s="3"/>
       <c r="P210" s="3"/>
       <c r="Q210" s="3"/>
@@ -10696,10 +10909,10 @@
       <c r="D211" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E211" s="59" t="s">
+      <c r="E211" s="60" t="s">
         <v>499</v>
       </c>
-      <c r="F211" s="59" t="s">
+      <c r="F211" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G211" s="10" t="s">
@@ -10720,6 +10933,7 @@
       <c r="M211" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="N211" s="11"/>
       <c r="O211" s="3"/>
       <c r="P211" s="3"/>
       <c r="Q211" s="3"/>
@@ -10742,10 +10956,10 @@
       <c r="D212" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E212" s="59" t="s">
+      <c r="E212" s="60" t="s">
         <v>502</v>
       </c>
-      <c r="F212" s="59" t="s">
+      <c r="F212" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G212" s="10" t="n">
@@ -10766,6 +10980,7 @@
       <c r="M212" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N212" s="11"/>
       <c r="O212" s="3"/>
       <c r="P212" s="3"/>
       <c r="Q212" s="3"/>
@@ -10788,10 +11003,10 @@
       <c r="D213" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E213" s="59" t="s">
+      <c r="E213" s="60" t="s">
         <v>504</v>
       </c>
-      <c r="F213" s="59" t="s">
+      <c r="F213" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G213" s="10" t="n">
@@ -10812,6 +11027,7 @@
       <c r="M213" s="10" t="n">
         <v>0.001</v>
       </c>
+      <c r="N213" s="11"/>
       <c r="O213" s="3"/>
       <c r="P213" s="3"/>
       <c r="Q213" s="3"/>
@@ -10834,10 +11050,10 @@
       <c r="D214" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E214" s="59" t="s">
+      <c r="E214" s="60" t="s">
         <v>506</v>
       </c>
-      <c r="F214" s="59" t="s">
+      <c r="F214" s="60" t="s">
         <v>507</v>
       </c>
       <c r="G214" s="10" t="n">
@@ -10864,14 +11080,15 @@
         <f aca="false">1250*0.000001/5</f>
         <v>0.00025</v>
       </c>
-      <c r="O214" s="58"/>
-      <c r="P214" s="58"/>
-      <c r="Q214" s="58"/>
-      <c r="R214" s="58"/>
-      <c r="S214" s="58"/>
-      <c r="T214" s="58"/>
-      <c r="U214" s="58"/>
-      <c r="V214" s="58"/>
+      <c r="N214" s="11"/>
+      <c r="O214" s="59"/>
+      <c r="P214" s="59"/>
+      <c r="Q214" s="59"/>
+      <c r="R214" s="59"/>
+      <c r="S214" s="59"/>
+      <c r="T214" s="59"/>
+      <c r="U214" s="59"/>
+      <c r="V214" s="59"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
@@ -10886,10 +11103,10 @@
       <c r="D215" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E215" s="59" t="s">
+      <c r="E215" s="60" t="s">
         <v>509</v>
       </c>
-      <c r="F215" s="59" t="s">
+      <c r="F215" s="60" t="s">
         <v>510</v>
       </c>
       <c r="G215" s="10" t="n">
@@ -10910,14 +11127,15 @@
       <c r="M215" s="10" t="n">
         <v>0.0002</v>
       </c>
-      <c r="O215" s="58"/>
-      <c r="P215" s="58"/>
-      <c r="Q215" s="58"/>
-      <c r="R215" s="58"/>
-      <c r="S215" s="58"/>
-      <c r="T215" s="58"/>
-      <c r="U215" s="58"/>
-      <c r="V215" s="58"/>
+      <c r="N215" s="11"/>
+      <c r="O215" s="59"/>
+      <c r="P215" s="59"/>
+      <c r="Q215" s="59"/>
+      <c r="R215" s="59"/>
+      <c r="S215" s="59"/>
+      <c r="T215" s="59"/>
+      <c r="U215" s="59"/>
+      <c r="V215" s="59"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4" t="s">
@@ -10932,10 +11150,10 @@
       <c r="D216" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E216" s="59" t="s">
+      <c r="E216" s="60" t="s">
         <v>512</v>
       </c>
-      <c r="F216" s="59" t="s">
+      <c r="F216" s="60" t="s">
         <v>513</v>
       </c>
       <c r="G216" s="10" t="n">
@@ -10958,17 +11176,18 @@
         <v>2.5E-012</v>
       </c>
       <c r="M216" s="10" t="n">
-        <f aca="false">0.0000000000025*10</f>
-        <v>2.5E-011</v>
-      </c>
-      <c r="O216" s="58"/>
-      <c r="P216" s="58"/>
-      <c r="Q216" s="58"/>
-      <c r="R216" s="58"/>
-      <c r="S216" s="58"/>
-      <c r="T216" s="58"/>
-      <c r="U216" s="58"/>
-      <c r="V216" s="58"/>
+        <f aca="false">0.0000000000025</f>
+        <v>2.5E-012</v>
+      </c>
+      <c r="N216" s="11"/>
+      <c r="O216" s="59"/>
+      <c r="P216" s="59"/>
+      <c r="Q216" s="59"/>
+      <c r="R216" s="59"/>
+      <c r="S216" s="59"/>
+      <c r="T216" s="59"/>
+      <c r="U216" s="59"/>
+      <c r="V216" s="59"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
@@ -10983,10 +11202,10 @@
       <c r="D217" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E217" s="59" t="s">
+      <c r="E217" s="60" t="s">
         <v>515</v>
       </c>
-      <c r="F217" s="59" t="s">
+      <c r="F217" s="60" t="s">
         <v>513</v>
       </c>
       <c r="G217" s="10" t="n">
@@ -11012,14 +11231,15 @@
         <f aca="false">M164</f>
         <v>5E-013</v>
       </c>
-      <c r="O217" s="58"/>
-      <c r="P217" s="58"/>
-      <c r="Q217" s="58"/>
-      <c r="R217" s="58"/>
-      <c r="S217" s="58"/>
-      <c r="T217" s="58"/>
-      <c r="U217" s="58"/>
-      <c r="V217" s="58"/>
+      <c r="N217" s="11"/>
+      <c r="O217" s="59"/>
+      <c r="P217" s="59"/>
+      <c r="Q217" s="59"/>
+      <c r="R217" s="59"/>
+      <c r="S217" s="59"/>
+      <c r="T217" s="59"/>
+      <c r="U217" s="59"/>
+      <c r="V217" s="59"/>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4" t="s">
@@ -11034,10 +11254,10 @@
       <c r="D218" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E218" s="59" t="s">
+      <c r="E218" s="60" t="s">
         <v>517</v>
       </c>
-      <c r="F218" s="59" t="s">
+      <c r="F218" s="60" t="s">
         <v>513</v>
       </c>
       <c r="G218" s="10" t="n">
@@ -11063,14 +11283,15 @@
         <f aca="false">0.00000000005 *2</f>
         <v>1E-010</v>
       </c>
-      <c r="O218" s="58"/>
-      <c r="P218" s="58"/>
-      <c r="Q218" s="58"/>
-      <c r="R218" s="58"/>
-      <c r="S218" s="58"/>
-      <c r="T218" s="58"/>
-      <c r="U218" s="58"/>
-      <c r="V218" s="58"/>
+      <c r="N218" s="11"/>
+      <c r="O218" s="59"/>
+      <c r="P218" s="59"/>
+      <c r="Q218" s="59"/>
+      <c r="R218" s="59"/>
+      <c r="S218" s="59"/>
+      <c r="T218" s="59"/>
+      <c r="U218" s="59"/>
+      <c r="V218" s="59"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
@@ -11085,10 +11306,10 @@
       <c r="D219" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E219" s="59" t="s">
+      <c r="E219" s="60" t="s">
         <v>517</v>
       </c>
-      <c r="F219" s="59" t="s">
+      <c r="F219" s="60" t="s">
         <v>513</v>
       </c>
       <c r="G219" s="10" t="n">
@@ -11114,14 +11335,15 @@
         <f aca="false">M218</f>
         <v>1E-010</v>
       </c>
-      <c r="O219" s="58"/>
-      <c r="P219" s="58"/>
-      <c r="Q219" s="58"/>
-      <c r="R219" s="58"/>
-      <c r="S219" s="58"/>
-      <c r="T219" s="58"/>
-      <c r="U219" s="58"/>
-      <c r="V219" s="58"/>
+      <c r="N219" s="11"/>
+      <c r="O219" s="59"/>
+      <c r="P219" s="59"/>
+      <c r="Q219" s="59"/>
+      <c r="R219" s="59"/>
+      <c r="S219" s="59"/>
+      <c r="T219" s="59"/>
+      <c r="U219" s="59"/>
+      <c r="V219" s="59"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="4" t="s">
@@ -11136,10 +11358,10 @@
       <c r="D220" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E220" s="59" t="s">
+      <c r="E220" s="60" t="s">
         <v>517</v>
       </c>
-      <c r="F220" s="59" t="s">
+      <c r="F220" s="60" t="s">
         <v>520</v>
       </c>
       <c r="G220" s="10"/>
@@ -11159,14 +11381,15 @@
       <c r="M220" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O220" s="58"/>
-      <c r="P220" s="58"/>
-      <c r="Q220" s="58"/>
-      <c r="R220" s="58"/>
-      <c r="S220" s="58"/>
-      <c r="T220" s="58"/>
-      <c r="U220" s="58"/>
-      <c r="V220" s="58"/>
+      <c r="N220" s="11"/>
+      <c r="O220" s="59"/>
+      <c r="P220" s="59"/>
+      <c r="Q220" s="59"/>
+      <c r="R220" s="59"/>
+      <c r="S220" s="59"/>
+      <c r="T220" s="59"/>
+      <c r="U220" s="59"/>
+      <c r="V220" s="59"/>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="s">
@@ -11181,10 +11404,10 @@
       <c r="D221" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E221" s="59" t="s">
+      <c r="E221" s="60" t="s">
         <v>522</v>
       </c>
-      <c r="F221" s="59" t="s">
+      <c r="F221" s="60" t="s">
         <v>497</v>
       </c>
       <c r="G221" s="10"/>
@@ -11208,14 +11431,15 @@
         <f aca="false">100</f>
         <v>100</v>
       </c>
-      <c r="O221" s="58"/>
-      <c r="P221" s="58"/>
-      <c r="Q221" s="58"/>
-      <c r="R221" s="58"/>
-      <c r="S221" s="58"/>
-      <c r="T221" s="58"/>
-      <c r="U221" s="58"/>
-      <c r="V221" s="58"/>
+      <c r="N221" s="11"/>
+      <c r="O221" s="59"/>
+      <c r="P221" s="59"/>
+      <c r="Q221" s="59"/>
+      <c r="R221" s="59"/>
+      <c r="S221" s="59"/>
+      <c r="T221" s="59"/>
+      <c r="U221" s="59"/>
+      <c r="V221" s="59"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="4" t="s">
@@ -11230,10 +11454,10 @@
       <c r="D222" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E222" s="59" t="s">
+      <c r="E222" s="60" t="s">
         <v>524</v>
       </c>
-      <c r="F222" s="59" t="s">
+      <c r="F222" s="60" t="s">
         <v>525</v>
       </c>
       <c r="G222" s="10" t="n">
@@ -11259,14 +11483,15 @@
         <f aca="false">0.000001 / 10000 / 4 / 10 /5</f>
         <v>5E-013</v>
       </c>
-      <c r="O222" s="58"/>
-      <c r="P222" s="58"/>
-      <c r="Q222" s="58"/>
-      <c r="R222" s="58"/>
-      <c r="S222" s="58"/>
-      <c r="T222" s="58"/>
-      <c r="U222" s="58"/>
-      <c r="V222" s="58"/>
+      <c r="N222" s="11"/>
+      <c r="O222" s="59"/>
+      <c r="P222" s="59"/>
+      <c r="Q222" s="59"/>
+      <c r="R222" s="59"/>
+      <c r="S222" s="59"/>
+      <c r="T222" s="59"/>
+      <c r="U222" s="59"/>
+      <c r="V222" s="59"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
@@ -11281,10 +11506,10 @@
       <c r="D223" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E223" s="59" t="s">
+      <c r="E223" s="60" t="s">
         <v>524</v>
       </c>
-      <c r="F223" s="59" t="s">
+      <c r="F223" s="60" t="s">
         <v>525</v>
       </c>
       <c r="G223" s="10" t="n">
@@ -11305,14 +11530,15 @@
       <c r="M223" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O223" s="58"/>
-      <c r="P223" s="58"/>
-      <c r="Q223" s="58"/>
-      <c r="R223" s="58"/>
-      <c r="S223" s="58"/>
-      <c r="T223" s="58"/>
-      <c r="U223" s="58"/>
-      <c r="V223" s="58"/>
+      <c r="N223" s="11"/>
+      <c r="O223" s="59"/>
+      <c r="P223" s="59"/>
+      <c r="Q223" s="59"/>
+      <c r="R223" s="59"/>
+      <c r="S223" s="59"/>
+      <c r="T223" s="59"/>
+      <c r="U223" s="59"/>
+      <c r="V223" s="59"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4" t="s">
@@ -11327,10 +11553,10 @@
       <c r="D224" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E224" s="59" t="s">
+      <c r="E224" s="60" t="s">
         <v>528</v>
       </c>
-      <c r="F224" s="59" t="s">
+      <c r="F224" s="60" t="s">
         <v>520</v>
       </c>
       <c r="G224" s="10" t="n">
@@ -11354,17 +11580,18 @@
         <v>6E-007</v>
       </c>
       <c r="M224" s="10" t="n">
-        <f aca="false">0.00001 / 10 / 5 / 10 * 6</f>
-        <v>1.2E-007</v>
-      </c>
-      <c r="O224" s="58"/>
-      <c r="P224" s="58"/>
-      <c r="Q224" s="58"/>
-      <c r="R224" s="58"/>
-      <c r="S224" s="58"/>
-      <c r="T224" s="58"/>
-      <c r="U224" s="58"/>
-      <c r="V224" s="58"/>
+        <f aca="false">0.00001 / 10 / 5 / 10 * 6 * 100</f>
+        <v>1.2E-005</v>
+      </c>
+      <c r="N224" s="11"/>
+      <c r="O224" s="59"/>
+      <c r="P224" s="59"/>
+      <c r="Q224" s="59"/>
+      <c r="R224" s="59"/>
+      <c r="S224" s="59"/>
+      <c r="T224" s="59"/>
+      <c r="U224" s="59"/>
+      <c r="V224" s="59"/>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
@@ -11379,10 +11606,10 @@
       <c r="D225" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E225" s="59" t="s">
+      <c r="E225" s="60" t="s">
         <v>530</v>
       </c>
-      <c r="F225" s="59" t="s">
+      <c r="F225" s="60" t="s">
         <v>520</v>
       </c>
       <c r="G225" s="10"/>
@@ -11406,14 +11633,15 @@
         <f aca="false">0.001</f>
         <v>0.001</v>
       </c>
-      <c r="O225" s="58"/>
-      <c r="P225" s="58"/>
-      <c r="Q225" s="58"/>
-      <c r="R225" s="58"/>
-      <c r="S225" s="58"/>
-      <c r="T225" s="58"/>
-      <c r="U225" s="58"/>
-      <c r="V225" s="58"/>
+      <c r="N225" s="11"/>
+      <c r="O225" s="59"/>
+      <c r="P225" s="59"/>
+      <c r="Q225" s="59"/>
+      <c r="R225" s="59"/>
+      <c r="S225" s="59"/>
+      <c r="T225" s="59"/>
+      <c r="U225" s="59"/>
+      <c r="V225" s="59"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4" t="s">
@@ -11428,13 +11656,13 @@
       <c r="D226" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E226" s="59" t="s">
+      <c r="E226" s="60" t="s">
         <v>532</v>
       </c>
-      <c r="F226" s="59" t="s">
+      <c r="F226" s="60" t="s">
         <v>520</v>
       </c>
-      <c r="G226" s="60" t="n">
+      <c r="G226" s="61" t="n">
         <v>1E-005</v>
       </c>
       <c r="I226" s="10" t="n">
@@ -11457,17 +11685,18 @@
         <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
         <v>1.2E-005</v>
       </c>
-      <c r="O226" s="58"/>
-      <c r="P226" s="58"/>
-      <c r="Q226" s="58"/>
-      <c r="R226" s="58"/>
-      <c r="S226" s="58"/>
-      <c r="T226" s="58"/>
-      <c r="U226" s="58"/>
-      <c r="V226" s="58"/>
+      <c r="N226" s="11"/>
+      <c r="O226" s="59"/>
+      <c r="P226" s="59"/>
+      <c r="Q226" s="59"/>
+      <c r="R226" s="59"/>
+      <c r="S226" s="59"/>
+      <c r="T226" s="59"/>
+      <c r="U226" s="59"/>
+      <c r="V226" s="59"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="61" t="s">
+      <c r="A227" s="62" t="s">
         <v>533</v>
       </c>
       <c r="B227" s="8" t="s">
@@ -11479,10 +11708,10 @@
       <c r="D227" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="E227" s="59" t="s">
+      <c r="E227" s="60" t="s">
         <v>535</v>
       </c>
-      <c r="F227" s="59" t="s">
+      <c r="F227" s="60" t="s">
         <v>35</v>
       </c>
       <c r="G227" s="10" t="s">
@@ -11503,6 +11732,7 @@
       <c r="M227" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N227" s="11"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4" t="s">
@@ -11517,10 +11747,10 @@
       <c r="D228" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E228" s="59" t="s">
+      <c r="E228" s="60" t="s">
         <v>537</v>
       </c>
-      <c r="F228" s="59" t="s">
+      <c r="F228" s="60" t="s">
         <v>497</v>
       </c>
       <c r="G228" s="10" t="n">
@@ -11541,6 +11771,7 @@
       <c r="M228" s="10" t="n">
         <v>0.2</v>
       </c>
+      <c r="N228" s="11"/>
       <c r="O228" s="3"/>
       <c r="P228" s="3"/>
       <c r="Q228" s="3"/>
@@ -11578,10 +11809,10 @@
       <c r="D229" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E229" s="59" t="s">
+      <c r="E229" s="60" t="s">
         <v>539</v>
       </c>
-      <c r="F229" s="59" t="s">
+      <c r="F229" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G229" s="10" t="s">
@@ -11602,6 +11833,7 @@
       <c r="M229" s="10" t="s">
         <v>25</v>
       </c>
+      <c r="N229" s="11"/>
       <c r="O229" s="3"/>
       <c r="P229" s="3"/>
       <c r="Q229" s="3"/>
@@ -11639,10 +11871,10 @@
       <c r="D230" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E230" s="59" t="s">
+      <c r="E230" s="60" t="s">
         <v>541</v>
       </c>
-      <c r="F230" s="59" t="s">
+      <c r="F230" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G230" s="10" t="n">
@@ -11669,6 +11901,7 @@
         <f aca="false">2*0.1</f>
         <v>0.2</v>
       </c>
+      <c r="N230" s="11"/>
       <c r="O230" s="3"/>
       <c r="P230" s="3"/>
       <c r="Q230" s="3"/>
@@ -11706,10 +11939,10 @@
       <c r="D231" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E231" s="59" t="s">
+      <c r="E231" s="60" t="s">
         <v>543</v>
       </c>
-      <c r="F231" s="59" t="s">
+      <c r="F231" s="60" t="s">
         <v>500</v>
       </c>
       <c r="G231" s="10" t="n">
@@ -11730,6 +11963,7 @@
       <c r="M231" s="10" t="n">
         <v>0.001</v>
       </c>
+      <c r="N231" s="11"/>
       <c r="O231" s="3"/>
       <c r="P231" s="3"/>
       <c r="Q231" s="3"/>
@@ -11767,10 +12001,10 @@
       <c r="D232" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E232" s="59" t="s">
+      <c r="E232" s="60" t="s">
         <v>545</v>
       </c>
-      <c r="F232" s="59" t="s">
+      <c r="F232" s="60" t="s">
         <v>546</v>
       </c>
       <c r="G232" s="10" t="n">
@@ -11796,29 +12030,30 @@
         <f aca="false">0.00001 / 2</f>
         <v>5E-006</v>
       </c>
-      <c r="O232" s="62"/>
-      <c r="P232" s="62"/>
-      <c r="Q232" s="62"/>
-      <c r="R232" s="62"/>
-      <c r="S232" s="62"/>
-      <c r="T232" s="62"/>
-      <c r="U232" s="62"/>
-      <c r="V232" s="62"/>
-      <c r="W232" s="62"/>
-      <c r="X232" s="62"/>
-      <c r="Y232" s="62"/>
+      <c r="N232" s="11"/>
+      <c r="O232" s="63"/>
+      <c r="P232" s="63"/>
+      <c r="Q232" s="63"/>
+      <c r="R232" s="63"/>
+      <c r="S232" s="63"/>
+      <c r="T232" s="63"/>
+      <c r="U232" s="63"/>
+      <c r="V232" s="63"/>
+      <c r="W232" s="63"/>
+      <c r="X232" s="63"/>
+      <c r="Y232" s="63"/>
       <c r="Z232" s="1"/>
-      <c r="AA232" s="62"/>
-      <c r="AB232" s="62"/>
-      <c r="AC232" s="62"/>
-      <c r="AD232" s="62"/>
-      <c r="AE232" s="62"/>
-      <c r="AF232" s="62"/>
-      <c r="AG232" s="62"/>
-      <c r="AH232" s="62"/>
-      <c r="AI232" s="62"/>
-      <c r="AJ232" s="62"/>
-      <c r="AK232" s="62"/>
+      <c r="AA232" s="63"/>
+      <c r="AB232" s="63"/>
+      <c r="AC232" s="63"/>
+      <c r="AD232" s="63"/>
+      <c r="AE232" s="63"/>
+      <c r="AF232" s="63"/>
+      <c r="AG232" s="63"/>
+      <c r="AH232" s="63"/>
+      <c r="AI232" s="63"/>
+      <c r="AJ232" s="63"/>
+      <c r="AK232" s="63"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4" t="s">
@@ -11833,13 +12068,13 @@
       <c r="D233" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E233" s="59" t="s">
+      <c r="E233" s="60" t="s">
         <v>548</v>
       </c>
-      <c r="F233" s="59" t="s">
+      <c r="F233" s="60" t="s">
         <v>500</v>
       </c>
-      <c r="G233" s="63" t="n">
+      <c r="G233" s="64" t="n">
         <v>1E-005</v>
       </c>
       <c r="I233" s="10" t="n">
@@ -11862,29 +12097,30 @@
         <f aca="false">0.000000005 / 5</f>
         <v>1E-009</v>
       </c>
-      <c r="O233" s="62"/>
-      <c r="P233" s="62"/>
-      <c r="Q233" s="62"/>
-      <c r="R233" s="62"/>
-      <c r="S233" s="62"/>
-      <c r="T233" s="62"/>
-      <c r="U233" s="62"/>
-      <c r="V233" s="62"/>
-      <c r="W233" s="62"/>
-      <c r="X233" s="62"/>
-      <c r="Y233" s="62"/>
+      <c r="N233" s="11"/>
+      <c r="O233" s="63"/>
+      <c r="P233" s="63"/>
+      <c r="Q233" s="63"/>
+      <c r="R233" s="63"/>
+      <c r="S233" s="63"/>
+      <c r="T233" s="63"/>
+      <c r="U233" s="63"/>
+      <c r="V233" s="63"/>
+      <c r="W233" s="63"/>
+      <c r="X233" s="63"/>
+      <c r="Y233" s="63"/>
       <c r="Z233" s="1"/>
-      <c r="AA233" s="62"/>
-      <c r="AB233" s="62"/>
-      <c r="AC233" s="62"/>
-      <c r="AD233" s="62"/>
-      <c r="AE233" s="62"/>
-      <c r="AF233" s="62"/>
-      <c r="AG233" s="62"/>
-      <c r="AH233" s="62"/>
-      <c r="AI233" s="62"/>
-      <c r="AJ233" s="62"/>
-      <c r="AK233" s="62"/>
+      <c r="AA233" s="63"/>
+      <c r="AB233" s="63"/>
+      <c r="AC233" s="63"/>
+      <c r="AD233" s="63"/>
+      <c r="AE233" s="63"/>
+      <c r="AF233" s="63"/>
+      <c r="AG233" s="63"/>
+      <c r="AH233" s="63"/>
+      <c r="AI233" s="63"/>
+      <c r="AJ233" s="63"/>
+      <c r="AK233" s="63"/>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4" t="s">
@@ -11899,10 +12135,10 @@
       <c r="D234" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E234" s="54" t="s">
+      <c r="E234" s="55" t="s">
         <v>490</v>
       </c>
-      <c r="F234" s="54" t="s">
+      <c r="F234" s="55" t="s">
         <v>491</v>
       </c>
       <c r="G234" s="10" t="n">
@@ -11924,6 +12160,7 @@
       <c r="M234" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N234" s="11"/>
       <c r="O234" s="1"/>
       <c r="P234" s="1"/>
       <c r="Q234" s="1"/>
@@ -11946,10 +12183,10 @@
       <c r="D235" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E235" s="54" t="s">
+      <c r="E235" s="55" t="s">
         <v>490</v>
       </c>
-      <c r="F235" s="54" t="s">
+      <c r="F235" s="55" t="s">
         <v>491</v>
       </c>
       <c r="G235" s="10" t="n">
@@ -11971,6 +12208,7 @@
       <c r="M235" s="10" t="n">
         <v>0</v>
       </c>
+      <c r="N235" s="11"/>
       <c r="O235" s="1"/>
       <c r="P235" s="1"/>
       <c r="Q235" s="1"/>
@@ -11993,10 +12231,10 @@
       <c r="D236" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E236" s="54" t="s">
+      <c r="E236" s="55" t="s">
         <v>552</v>
       </c>
-      <c r="F236" s="54" t="s">
+      <c r="F236" s="55" t="s">
         <v>265</v>
       </c>
       <c r="G236" s="10" t="n">
@@ -12017,6 +12255,7 @@
       <c r="M236" s="10" t="s">
         <v>36</v>
       </c>
+      <c r="N236" s="11"/>
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
       <c r="Q236" s="1"/>
@@ -12027,7 +12266,7 @@
       <c r="V236" s="1"/>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="42" t="s">
+      <c r="A237" s="43" t="s">
         <v>553</v>
       </c>
       <c r="B237" s="8" t="s">
@@ -12039,10 +12278,10 @@
       <c r="D237" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E237" s="43" t="s">
+      <c r="E237" s="44" t="s">
         <v>554</v>
       </c>
-      <c r="F237" s="43" t="s">
+      <c r="F237" s="44" t="s">
         <v>555</v>
       </c>
       <c r="G237" s="10" t="n">
@@ -12068,9 +12307,10 @@
         <f aca="false">0.0000000000005* (6 * 12 / 0.44) * 0.0173 / 14 / 1.4 / 10 / 2 /2</f>
         <v>1.805426716141E-015</v>
       </c>
+      <c r="N237" s="11"/>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="42" t="s">
+      <c r="A238" s="43" t="s">
         <v>556</v>
       </c>
       <c r="B238" s="8" t="s">
@@ -12082,10 +12322,10 @@
       <c r="D238" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E238" s="43" t="s">
+      <c r="E238" s="44" t="s">
         <v>554</v>
       </c>
-      <c r="F238" s="43" t="s">
+      <c r="F238" s="44" t="s">
         <v>555</v>
       </c>
       <c r="G238" s="10" t="n">
@@ -12111,6 +12351,7 @@
         <f aca="false">0.000001/3600/10/10</f>
         <v>2.77777777777778E-012</v>
       </c>
+      <c r="N238" s="11"/>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4" t="s">
@@ -12125,13 +12366,13 @@
       <c r="D239" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E239" s="59" t="s">
+      <c r="E239" s="60" t="s">
         <v>558</v>
       </c>
-      <c r="F239" s="59" t="s">
+      <c r="F239" s="60" t="s">
         <v>559</v>
       </c>
-      <c r="G239" s="59" t="n">
+      <c r="G239" s="60" t="n">
         <v>0.1</v>
       </c>
       <c r="I239" s="10" t="n">
@@ -12149,6 +12390,7 @@
       <c r="M239" s="10" t="n">
         <v>0.01</v>
       </c>
+      <c r="N239" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I239:L239">
@@ -12283,7 +12525,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:X4 AW4 G4 P4:R4 I4:L4 N4">
+  <conditionalFormatting sqref="U4:X4 AW4 G4 P4:R4 I4:L4">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -12327,7 +12569,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I216:L216">
+  <conditionalFormatting sqref="I216:M216">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -17025,7 +17267,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I224:L224">
+  <conditionalFormatting sqref="I224:M224">
     <cfRule type="colorScale" priority="445">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22107,7 +22349,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M216">
+  <conditionalFormatting sqref="M2">
     <cfRule type="colorScale" priority="907">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22129,7 +22371,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
+  <conditionalFormatting sqref="M3 M5">
     <cfRule type="colorScale" priority="909">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22151,7 +22393,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3 M5">
+  <conditionalFormatting sqref="M6 M227">
     <cfRule type="colorScale" priority="911">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22173,7 +22415,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6 M227">
+  <conditionalFormatting sqref="M7">
     <cfRule type="colorScale" priority="913">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22195,7 +22437,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7">
+  <conditionalFormatting sqref="M8">
     <cfRule type="colorScale" priority="915">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22217,7 +22459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M8">
+  <conditionalFormatting sqref="M9">
     <cfRule type="colorScale" priority="917">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22239,7 +22481,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9">
+  <conditionalFormatting sqref="M10">
     <cfRule type="colorScale" priority="919">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22261,7 +22503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10">
+  <conditionalFormatting sqref="M11">
     <cfRule type="colorScale" priority="921">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22283,7 +22525,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M11">
+  <conditionalFormatting sqref="M12">
     <cfRule type="colorScale" priority="923">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22305,7 +22547,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M12">
+  <conditionalFormatting sqref="M13">
     <cfRule type="colorScale" priority="925">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22327,7 +22569,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M13">
+  <conditionalFormatting sqref="M14">
     <cfRule type="colorScale" priority="927">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22349,7 +22591,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M14">
+  <conditionalFormatting sqref="M15">
     <cfRule type="colorScale" priority="929">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22371,7 +22613,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M15">
+  <conditionalFormatting sqref="M16">
     <cfRule type="colorScale" priority="931">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22393,7 +22635,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M16">
+  <conditionalFormatting sqref="M17">
     <cfRule type="colorScale" priority="933">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22415,7 +22657,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M17">
+  <conditionalFormatting sqref="M18">
     <cfRule type="colorScale" priority="935">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22437,7 +22679,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M18">
+  <conditionalFormatting sqref="M19">
     <cfRule type="colorScale" priority="937">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22459,7 +22701,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M19">
+  <conditionalFormatting sqref="M20">
     <cfRule type="colorScale" priority="939">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22481,7 +22723,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M20">
+  <conditionalFormatting sqref="M21">
     <cfRule type="colorScale" priority="941">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22503,7 +22745,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M21">
+  <conditionalFormatting sqref="M22">
     <cfRule type="colorScale" priority="943">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22525,7 +22767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M22">
+  <conditionalFormatting sqref="M23">
     <cfRule type="colorScale" priority="945">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22547,7 +22789,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M23">
+  <conditionalFormatting sqref="M24:M25">
     <cfRule type="colorScale" priority="947">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22569,7 +22811,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M24:M25">
+  <conditionalFormatting sqref="M26">
     <cfRule type="colorScale" priority="949">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22591,7 +22833,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M26">
+  <conditionalFormatting sqref="M27">
     <cfRule type="colorScale" priority="951">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22613,7 +22855,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M27">
+  <conditionalFormatting sqref="M28">
     <cfRule type="colorScale" priority="953">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22635,7 +22877,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M28">
+  <conditionalFormatting sqref="M29">
     <cfRule type="colorScale" priority="955">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22657,7 +22899,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M29">
+  <conditionalFormatting sqref="M30">
     <cfRule type="colorScale" priority="957">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22679,7 +22921,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M30">
+  <conditionalFormatting sqref="M31">
     <cfRule type="colorScale" priority="959">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22701,7 +22943,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M31">
+  <conditionalFormatting sqref="M32">
     <cfRule type="colorScale" priority="961">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22723,7 +22965,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M32">
+  <conditionalFormatting sqref="M33">
     <cfRule type="colorScale" priority="963">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22745,7 +22987,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
+  <conditionalFormatting sqref="M34">
     <cfRule type="colorScale" priority="965">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22767,7 +23009,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34">
+  <conditionalFormatting sqref="M35">
     <cfRule type="colorScale" priority="967">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22789,7 +23031,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M35">
+  <conditionalFormatting sqref="M36">
     <cfRule type="colorScale" priority="969">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22811,7 +23053,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M36">
+  <conditionalFormatting sqref="M37">
     <cfRule type="colorScale" priority="971">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22833,7 +23075,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
+  <conditionalFormatting sqref="M38">
     <cfRule type="colorScale" priority="973">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22855,7 +23097,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M38">
+  <conditionalFormatting sqref="M39">
     <cfRule type="colorScale" priority="975">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22877,7 +23119,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M39">
+  <conditionalFormatting sqref="M40">
     <cfRule type="colorScale" priority="977">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22899,7 +23141,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M40">
+  <conditionalFormatting sqref="M41">
     <cfRule type="colorScale" priority="979">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22921,7 +23163,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M41">
+  <conditionalFormatting sqref="M42">
     <cfRule type="colorScale" priority="981">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22943,7 +23185,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M42">
+  <conditionalFormatting sqref="M43">
     <cfRule type="colorScale" priority="983">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22965,7 +23207,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M43">
+  <conditionalFormatting sqref="M44">
     <cfRule type="colorScale" priority="985">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -22987,7 +23229,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M44">
+  <conditionalFormatting sqref="M45">
     <cfRule type="colorScale" priority="987">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23009,7 +23251,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M45">
+  <conditionalFormatting sqref="M46">
     <cfRule type="colorScale" priority="989">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23031,7 +23273,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M46">
+  <conditionalFormatting sqref="M47">
     <cfRule type="colorScale" priority="991">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23053,7 +23295,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M47">
+  <conditionalFormatting sqref="M48">
     <cfRule type="colorScale" priority="993">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23075,7 +23317,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M48">
+  <conditionalFormatting sqref="M49">
     <cfRule type="colorScale" priority="995">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23097,7 +23339,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M49">
+  <conditionalFormatting sqref="M50">
     <cfRule type="colorScale" priority="997">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23119,7 +23361,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M50">
+  <conditionalFormatting sqref="M51">
     <cfRule type="colorScale" priority="999">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23141,7 +23383,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M51">
+  <conditionalFormatting sqref="M52">
     <cfRule type="colorScale" priority="1001">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23163,7 +23405,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M52">
+  <conditionalFormatting sqref="M53">
     <cfRule type="colorScale" priority="1003">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23185,7 +23427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M53">
+  <conditionalFormatting sqref="M54">
     <cfRule type="colorScale" priority="1005">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23207,7 +23449,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M54">
+  <conditionalFormatting sqref="M55">
     <cfRule type="colorScale" priority="1007">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23229,7 +23471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M55">
+  <conditionalFormatting sqref="M56">
     <cfRule type="colorScale" priority="1009">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23251,7 +23493,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M56">
+  <conditionalFormatting sqref="M57">
     <cfRule type="colorScale" priority="1011">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23273,7 +23515,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M57">
+  <conditionalFormatting sqref="M58">
     <cfRule type="colorScale" priority="1013">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23295,7 +23537,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M58">
+  <conditionalFormatting sqref="M59">
     <cfRule type="colorScale" priority="1015">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23317,7 +23559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M59">
+  <conditionalFormatting sqref="M60">
     <cfRule type="colorScale" priority="1017">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23339,7 +23581,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60">
+  <conditionalFormatting sqref="M61">
     <cfRule type="colorScale" priority="1019">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23361,7 +23603,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M61">
+  <conditionalFormatting sqref="M62">
     <cfRule type="colorScale" priority="1021">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23383,7 +23625,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M62">
+  <conditionalFormatting sqref="M63">
     <cfRule type="colorScale" priority="1023">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23405,7 +23647,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M63">
+  <conditionalFormatting sqref="M64">
     <cfRule type="colorScale" priority="1025">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23427,7 +23669,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M64">
+  <conditionalFormatting sqref="M65">
     <cfRule type="colorScale" priority="1027">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23449,7 +23691,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M65">
+  <conditionalFormatting sqref="M66">
     <cfRule type="colorScale" priority="1029">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23471,7 +23713,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M66">
+  <conditionalFormatting sqref="M67">
     <cfRule type="colorScale" priority="1031">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23493,7 +23735,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M67">
+  <conditionalFormatting sqref="M68">
     <cfRule type="colorScale" priority="1033">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23515,7 +23757,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M68">
+  <conditionalFormatting sqref="M69">
     <cfRule type="colorScale" priority="1035">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23537,7 +23779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M69">
+  <conditionalFormatting sqref="M70">
     <cfRule type="colorScale" priority="1037">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23559,7 +23801,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M70">
+  <conditionalFormatting sqref="M71">
     <cfRule type="colorScale" priority="1039">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23581,7 +23823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M71">
+  <conditionalFormatting sqref="M72">
     <cfRule type="colorScale" priority="1041">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23603,7 +23845,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M72">
+  <conditionalFormatting sqref="M73">
     <cfRule type="colorScale" priority="1043">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23625,7 +23867,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M73">
+  <conditionalFormatting sqref="M74">
     <cfRule type="colorScale" priority="1045">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23647,7 +23889,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M74">
+  <conditionalFormatting sqref="M75">
     <cfRule type="colorScale" priority="1047">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23669,7 +23911,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M75">
+  <conditionalFormatting sqref="M76">
     <cfRule type="colorScale" priority="1049">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23691,7 +23933,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M76">
+  <conditionalFormatting sqref="M77">
     <cfRule type="colorScale" priority="1051">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23713,7 +23955,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M77">
+  <conditionalFormatting sqref="M78">
     <cfRule type="colorScale" priority="1053">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23735,7 +23977,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M78">
+  <conditionalFormatting sqref="M79">
     <cfRule type="colorScale" priority="1055">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23757,7 +23999,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M79">
+  <conditionalFormatting sqref="M80">
     <cfRule type="colorScale" priority="1057">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23779,7 +24021,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M80">
+  <conditionalFormatting sqref="M81">
     <cfRule type="colorScale" priority="1059">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23801,7 +24043,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M81">
+  <conditionalFormatting sqref="M82">
     <cfRule type="colorScale" priority="1061">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23823,7 +24065,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M82">
+  <conditionalFormatting sqref="M83">
     <cfRule type="colorScale" priority="1063">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23845,7 +24087,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M83">
+  <conditionalFormatting sqref="M84">
     <cfRule type="colorScale" priority="1065">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23867,7 +24109,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M84">
+  <conditionalFormatting sqref="M85">
     <cfRule type="colorScale" priority="1067">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23889,7 +24131,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M85">
+  <conditionalFormatting sqref="M86">
     <cfRule type="colorScale" priority="1069">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23911,7 +24153,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M86">
+  <conditionalFormatting sqref="M87">
     <cfRule type="colorScale" priority="1071">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23933,7 +24175,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M87">
+  <conditionalFormatting sqref="M88">
     <cfRule type="colorScale" priority="1073">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23955,7 +24197,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M88">
+  <conditionalFormatting sqref="M89">
     <cfRule type="colorScale" priority="1075">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23977,7 +24219,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M89">
+  <conditionalFormatting sqref="M90">
     <cfRule type="colorScale" priority="1077">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -23999,7 +24241,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M90">
+  <conditionalFormatting sqref="M91">
     <cfRule type="colorScale" priority="1079">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24021,7 +24263,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M91">
+  <conditionalFormatting sqref="M92">
     <cfRule type="colorScale" priority="1081">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24043,7 +24285,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M92">
+  <conditionalFormatting sqref="M93">
     <cfRule type="colorScale" priority="1083">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24065,7 +24307,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M93">
+  <conditionalFormatting sqref="M94">
     <cfRule type="colorScale" priority="1085">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24087,7 +24329,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M94">
+  <conditionalFormatting sqref="M95">
     <cfRule type="colorScale" priority="1087">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24109,7 +24351,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M95">
+  <conditionalFormatting sqref="M96">
     <cfRule type="colorScale" priority="1089">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24131,7 +24373,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M96">
+  <conditionalFormatting sqref="M97">
     <cfRule type="colorScale" priority="1091">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24153,7 +24395,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M97">
+  <conditionalFormatting sqref="M98">
     <cfRule type="colorScale" priority="1093">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24175,7 +24417,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M98">
+  <conditionalFormatting sqref="M99">
     <cfRule type="colorScale" priority="1095">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24197,7 +24439,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M99">
+  <conditionalFormatting sqref="M100">
     <cfRule type="colorScale" priority="1097">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24219,7 +24461,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M100">
+  <conditionalFormatting sqref="M101">
     <cfRule type="colorScale" priority="1099">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24241,7 +24483,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M101">
+  <conditionalFormatting sqref="M102">
     <cfRule type="colorScale" priority="1101">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24263,7 +24505,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M102">
+  <conditionalFormatting sqref="M103">
     <cfRule type="colorScale" priority="1103">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24285,7 +24527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M103">
+  <conditionalFormatting sqref="M104">
     <cfRule type="colorScale" priority="1105">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24307,7 +24549,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M104">
+  <conditionalFormatting sqref="M105">
     <cfRule type="colorScale" priority="1107">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24329,7 +24571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M105">
+  <conditionalFormatting sqref="M106">
     <cfRule type="colorScale" priority="1109">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24351,7 +24593,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M106">
+  <conditionalFormatting sqref="M107">
     <cfRule type="colorScale" priority="1111">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24373,7 +24615,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M107">
+  <conditionalFormatting sqref="M108">
     <cfRule type="colorScale" priority="1113">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24395,7 +24637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M108">
+  <conditionalFormatting sqref="M109">
     <cfRule type="colorScale" priority="1115">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24417,7 +24659,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M109">
+  <conditionalFormatting sqref="M110">
     <cfRule type="colorScale" priority="1117">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24439,7 +24681,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M110">
+  <conditionalFormatting sqref="M111">
     <cfRule type="colorScale" priority="1119">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24461,7 +24703,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M111">
+  <conditionalFormatting sqref="M112">
     <cfRule type="colorScale" priority="1121">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24483,7 +24725,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M112">
+  <conditionalFormatting sqref="M113">
     <cfRule type="colorScale" priority="1123">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24505,7 +24747,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M113">
+  <conditionalFormatting sqref="M114">
     <cfRule type="colorScale" priority="1125">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24527,7 +24769,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M114">
+  <conditionalFormatting sqref="M115">
     <cfRule type="colorScale" priority="1127">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24549,7 +24791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M115">
+  <conditionalFormatting sqref="M116">
     <cfRule type="colorScale" priority="1129">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24571,7 +24813,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M116">
+  <conditionalFormatting sqref="M117">
     <cfRule type="colorScale" priority="1131">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24593,7 +24835,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M117">
+  <conditionalFormatting sqref="M118">
     <cfRule type="colorScale" priority="1133">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24615,7 +24857,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M118">
+  <conditionalFormatting sqref="M119">
     <cfRule type="colorScale" priority="1135">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24637,7 +24879,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M119">
+  <conditionalFormatting sqref="M120">
     <cfRule type="colorScale" priority="1137">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24659,7 +24901,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M120">
+  <conditionalFormatting sqref="M121">
     <cfRule type="colorScale" priority="1139">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24681,7 +24923,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M121">
+  <conditionalFormatting sqref="M122">
     <cfRule type="colorScale" priority="1141">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24703,7 +24945,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M122">
+  <conditionalFormatting sqref="M123">
     <cfRule type="colorScale" priority="1143">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24725,7 +24967,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M123">
+  <conditionalFormatting sqref="M124">
     <cfRule type="colorScale" priority="1145">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24747,7 +24989,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M124">
+  <conditionalFormatting sqref="M125">
     <cfRule type="colorScale" priority="1147">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24769,7 +25011,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M125">
+  <conditionalFormatting sqref="M126">
     <cfRule type="colorScale" priority="1149">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24791,7 +25033,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M126">
+  <conditionalFormatting sqref="M127">
     <cfRule type="colorScale" priority="1151">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24813,7 +25055,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M127">
+  <conditionalFormatting sqref="M128">
     <cfRule type="colorScale" priority="1153">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24835,7 +25077,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M128">
+  <conditionalFormatting sqref="M129:M130">
     <cfRule type="colorScale" priority="1155">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24857,7 +25099,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M129:M130">
+  <conditionalFormatting sqref="M131">
     <cfRule type="colorScale" priority="1157">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24879,7 +25121,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M131">
+  <conditionalFormatting sqref="M132">
     <cfRule type="colorScale" priority="1159">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24901,7 +25143,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M132">
+  <conditionalFormatting sqref="M133">
     <cfRule type="colorScale" priority="1161">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24923,7 +25165,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M133">
+  <conditionalFormatting sqref="M134">
     <cfRule type="colorScale" priority="1163">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24945,7 +25187,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M134">
+  <conditionalFormatting sqref="M135">
     <cfRule type="colorScale" priority="1165">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24967,7 +25209,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M135">
+  <conditionalFormatting sqref="M136">
     <cfRule type="colorScale" priority="1167">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24978,6 +25220,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M137">
     <cfRule type="colorScale" priority="1168">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -24988,8 +25232,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M136">
     <cfRule type="colorScale" priority="1169">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25001,7 +25243,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M137">
+  <conditionalFormatting sqref="M138">
     <cfRule type="colorScale" priority="1170">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25023,7 +25265,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M138">
+  <conditionalFormatting sqref="M139">
     <cfRule type="colorScale" priority="1172">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25045,7 +25287,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M139">
+  <conditionalFormatting sqref="M140">
     <cfRule type="colorScale" priority="1174">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25067,7 +25309,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M140">
+  <conditionalFormatting sqref="M141">
     <cfRule type="colorScale" priority="1176">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25089,7 +25331,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M141">
+  <conditionalFormatting sqref="M142">
     <cfRule type="colorScale" priority="1178">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25111,7 +25353,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M142">
+  <conditionalFormatting sqref="M143">
     <cfRule type="colorScale" priority="1180">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25133,7 +25375,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M143">
+  <conditionalFormatting sqref="M144">
     <cfRule type="colorScale" priority="1182">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25155,7 +25397,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M144">
+  <conditionalFormatting sqref="M145">
     <cfRule type="colorScale" priority="1184">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25177,7 +25419,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M145">
+  <conditionalFormatting sqref="M146">
     <cfRule type="colorScale" priority="1186">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25199,7 +25441,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M146">
+  <conditionalFormatting sqref="M147">
     <cfRule type="colorScale" priority="1188">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25221,7 +25463,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M147">
+  <conditionalFormatting sqref="M148">
     <cfRule type="colorScale" priority="1190">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25243,7 +25485,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M148">
+  <conditionalFormatting sqref="M149">
     <cfRule type="colorScale" priority="1192">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25265,7 +25507,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M149">
+  <conditionalFormatting sqref="M150">
     <cfRule type="colorScale" priority="1194">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25287,7 +25529,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M150">
+  <conditionalFormatting sqref="M151">
     <cfRule type="colorScale" priority="1196">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25309,7 +25551,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M151">
+  <conditionalFormatting sqref="M152">
     <cfRule type="colorScale" priority="1198">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25331,7 +25573,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M152">
+  <conditionalFormatting sqref="M153">
     <cfRule type="colorScale" priority="1200">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25353,7 +25595,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M153">
+  <conditionalFormatting sqref="M154">
     <cfRule type="colorScale" priority="1202">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25375,7 +25617,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M154">
+  <conditionalFormatting sqref="M155">
     <cfRule type="colorScale" priority="1204">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25397,7 +25639,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M155">
+  <conditionalFormatting sqref="M156">
     <cfRule type="colorScale" priority="1206">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25419,7 +25661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M156">
+  <conditionalFormatting sqref="M157">
     <cfRule type="colorScale" priority="1208">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25441,7 +25683,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M157">
+  <conditionalFormatting sqref="M158">
     <cfRule type="colorScale" priority="1210">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25463,7 +25705,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M158">
+  <conditionalFormatting sqref="M159">
     <cfRule type="colorScale" priority="1212">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25485,7 +25727,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M159">
+  <conditionalFormatting sqref="M160">
     <cfRule type="colorScale" priority="1214">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25507,7 +25749,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M160">
+  <conditionalFormatting sqref="M161">
     <cfRule type="colorScale" priority="1216">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25529,7 +25771,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M161">
+  <conditionalFormatting sqref="M162">
     <cfRule type="colorScale" priority="1218">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25551,7 +25793,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M162">
+  <conditionalFormatting sqref="M163">
     <cfRule type="colorScale" priority="1220">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25573,7 +25815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M163">
+  <conditionalFormatting sqref="M164">
     <cfRule type="colorScale" priority="1222">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25595,7 +25837,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M164">
+  <conditionalFormatting sqref="M165">
     <cfRule type="colorScale" priority="1224">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25617,7 +25859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M165">
+  <conditionalFormatting sqref="M166">
     <cfRule type="colorScale" priority="1226">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25639,7 +25881,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M166">
+  <conditionalFormatting sqref="M167">
     <cfRule type="colorScale" priority="1228">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25661,7 +25903,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M167">
+  <conditionalFormatting sqref="M168">
     <cfRule type="colorScale" priority="1230">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25683,7 +25925,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M168">
+  <conditionalFormatting sqref="M169">
     <cfRule type="colorScale" priority="1232">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25705,7 +25947,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M169">
+  <conditionalFormatting sqref="M170">
     <cfRule type="colorScale" priority="1234">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25727,7 +25969,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M170">
+  <conditionalFormatting sqref="M171">
     <cfRule type="colorScale" priority="1236">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25749,7 +25991,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M171">
+  <conditionalFormatting sqref="M172">
     <cfRule type="colorScale" priority="1238">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25771,7 +26013,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M172">
+  <conditionalFormatting sqref="M173">
     <cfRule type="colorScale" priority="1240">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25793,7 +26035,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M173">
+  <conditionalFormatting sqref="M174">
     <cfRule type="colorScale" priority="1242">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25815,7 +26057,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M174">
+  <conditionalFormatting sqref="M175">
     <cfRule type="colorScale" priority="1244">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25837,7 +26079,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M175">
+  <conditionalFormatting sqref="M176">
     <cfRule type="colorScale" priority="1246">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25859,7 +26101,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M176">
+  <conditionalFormatting sqref="M177">
     <cfRule type="colorScale" priority="1248">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25881,7 +26123,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M177">
+  <conditionalFormatting sqref="M178">
     <cfRule type="colorScale" priority="1250">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25903,7 +26145,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M178">
+  <conditionalFormatting sqref="M179">
     <cfRule type="colorScale" priority="1252">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25925,7 +26167,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M179">
+  <conditionalFormatting sqref="M180">
     <cfRule type="colorScale" priority="1254">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25947,7 +26189,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M180">
+  <conditionalFormatting sqref="M181">
     <cfRule type="colorScale" priority="1256">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25969,7 +26211,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M181">
+  <conditionalFormatting sqref="M182">
     <cfRule type="colorScale" priority="1258">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -25991,7 +26233,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M182">
+  <conditionalFormatting sqref="M183">
     <cfRule type="colorScale" priority="1260">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26013,7 +26255,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M183">
+  <conditionalFormatting sqref="M184">
     <cfRule type="colorScale" priority="1262">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26035,7 +26277,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M184">
+  <conditionalFormatting sqref="M185">
     <cfRule type="colorScale" priority="1264">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26057,7 +26299,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M185">
+  <conditionalFormatting sqref="M186">
     <cfRule type="colorScale" priority="1266">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26079,7 +26321,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M186">
+  <conditionalFormatting sqref="M187">
     <cfRule type="colorScale" priority="1268">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26101,7 +26343,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M187">
+  <conditionalFormatting sqref="M188">
     <cfRule type="colorScale" priority="1270">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26123,7 +26365,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M188">
+  <conditionalFormatting sqref="M189">
     <cfRule type="colorScale" priority="1272">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26145,7 +26387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M189">
+  <conditionalFormatting sqref="M190">
     <cfRule type="colorScale" priority="1274">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26167,7 +26409,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M190">
+  <conditionalFormatting sqref="M191">
     <cfRule type="colorScale" priority="1276">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26189,7 +26431,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M191">
+  <conditionalFormatting sqref="M192">
     <cfRule type="colorScale" priority="1278">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26211,7 +26453,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M192">
+  <conditionalFormatting sqref="M193">
     <cfRule type="colorScale" priority="1280">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26233,7 +26475,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M193">
+  <conditionalFormatting sqref="M194">
     <cfRule type="colorScale" priority="1282">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26255,7 +26497,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M194">
+  <conditionalFormatting sqref="M195">
     <cfRule type="colorScale" priority="1284">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26277,7 +26519,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M195">
+  <conditionalFormatting sqref="M196">
     <cfRule type="colorScale" priority="1286">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26299,7 +26541,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M196">
+  <conditionalFormatting sqref="M197">
     <cfRule type="colorScale" priority="1288">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26321,7 +26563,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M197">
+  <conditionalFormatting sqref="M198">
     <cfRule type="colorScale" priority="1290">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26343,7 +26585,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M198">
+  <conditionalFormatting sqref="M199">
     <cfRule type="colorScale" priority="1292">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26365,7 +26607,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M199">
+  <conditionalFormatting sqref="M200">
     <cfRule type="colorScale" priority="1294">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26387,7 +26629,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M200">
+  <conditionalFormatting sqref="M201">
     <cfRule type="colorScale" priority="1296">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26409,7 +26651,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M201">
+  <conditionalFormatting sqref="M202">
     <cfRule type="colorScale" priority="1298">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26431,7 +26673,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M202">
+  <conditionalFormatting sqref="M203">
     <cfRule type="colorScale" priority="1300">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26453,7 +26695,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M203">
+  <conditionalFormatting sqref="M204">
     <cfRule type="colorScale" priority="1302">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26475,7 +26717,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M204">
+  <conditionalFormatting sqref="M205">
     <cfRule type="colorScale" priority="1304">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26497,7 +26739,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M205">
+  <conditionalFormatting sqref="M206">
     <cfRule type="colorScale" priority="1306">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26519,7 +26761,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M206">
+  <conditionalFormatting sqref="M207">
     <cfRule type="colorScale" priority="1308">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26541,7 +26783,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M207">
+  <conditionalFormatting sqref="M208">
     <cfRule type="colorScale" priority="1310">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26563,7 +26805,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M208">
+  <conditionalFormatting sqref="M209">
     <cfRule type="colorScale" priority="1312">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26585,7 +26827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M209">
+  <conditionalFormatting sqref="M210">
     <cfRule type="colorScale" priority="1314">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26607,7 +26849,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M210">
+  <conditionalFormatting sqref="M211">
     <cfRule type="colorScale" priority="1316">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26629,7 +26871,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M211">
+  <conditionalFormatting sqref="M212">
     <cfRule type="colorScale" priority="1318">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26651,7 +26893,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M212">
+  <conditionalFormatting sqref="M213">
     <cfRule type="colorScale" priority="1320">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26673,7 +26915,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M213">
+  <conditionalFormatting sqref="M214:M215">
     <cfRule type="colorScale" priority="1322">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26695,7 +26937,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M214:M215">
+  <conditionalFormatting sqref="M217">
     <cfRule type="colorScale" priority="1324">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26717,7 +26959,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M217">
+  <conditionalFormatting sqref="M218:M219">
     <cfRule type="colorScale" priority="1326">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26739,7 +26981,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M218:M219">
+  <conditionalFormatting sqref="M220:M221">
     <cfRule type="colorScale" priority="1328">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26761,7 +27003,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M220:M221">
+  <conditionalFormatting sqref="M222:M223">
     <cfRule type="colorScale" priority="1330">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26783,7 +27025,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M222:M223">
+  <conditionalFormatting sqref="M225">
     <cfRule type="colorScale" priority="1332">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26805,7 +27047,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M224">
+  <conditionalFormatting sqref="M226">
     <cfRule type="colorScale" priority="1334">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26827,7 +27069,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M225">
+  <conditionalFormatting sqref="M228:M231">
     <cfRule type="colorScale" priority="1336">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26849,7 +27091,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M226">
+  <conditionalFormatting sqref="M234:M235">
     <cfRule type="colorScale" priority="1338">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26871,7 +27113,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M228:M231">
+  <conditionalFormatting sqref="M236">
     <cfRule type="colorScale" priority="1340">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26893,7 +27135,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M234:M235">
+  <conditionalFormatting sqref="M238">
     <cfRule type="colorScale" priority="1342">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -26905,50 +27147,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="1343">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M236">
-    <cfRule type="colorScale" priority="1344">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1345">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M238">
-    <cfRule type="colorScale" priority="1346">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1347">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>

--- a/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
+++ b/simulations/hydro/inputs/Scenarios_26-08-04.xlsx
@@ -11682,8 +11682,8 @@
         <v>0.00012</v>
       </c>
       <c r="M226" s="10" t="n">
-        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2</f>
-        <v>1.2E-005</v>
+        <f aca="false">0.00001 /5 /2/4 * 4 * 0.6 * 10*2 * 10</f>
+        <v>0.00012</v>
       </c>
       <c r="N226" s="11"/>
       <c r="O226" s="59"/>
@@ -17311,7 +17311,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I226:L226">
+  <conditionalFormatting sqref="I226:M226">
     <cfRule type="colorScale" priority="449">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -27047,7 +27047,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M226">
+  <conditionalFormatting sqref="M228:M231">
     <cfRule type="colorScale" priority="1334">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -27069,7 +27069,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M228:M231">
+  <conditionalFormatting sqref="M234:M235">
     <cfRule type="colorScale" priority="1336">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -27091,7 +27091,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M234:M235">
+  <conditionalFormatting sqref="M236">
     <cfRule type="colorScale" priority="1338">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -27113,7 +27113,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M236">
+  <conditionalFormatting sqref="M238">
     <cfRule type="colorScale" priority="1340">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -27125,28 +27125,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="1341">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M238">
-    <cfRule type="colorScale" priority="1342">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1343">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
